--- a/Matriz DOFA.xlsx
+++ b/Matriz DOFA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Osc\Mintic\Proyecto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{664C4F7E-5C91-4283-8BDE-E34FC34E65C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60A7B162-0D46-4545-B323-127115E139DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Matriz EFI" sheetId="4" r:id="rId1"/>
@@ -1623,45 +1623,6 @@
     <xf numFmtId="0" fontId="13" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="28" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="29" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="34" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="13" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
@@ -1674,40 +1635,13 @@
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="justify" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="justify"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
@@ -1745,18 +1679,6 @@
     <xf numFmtId="1" fontId="12" fillId="6" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="16" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="26" fillId="5" borderId="38" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -1764,10 +1686,6 @@
     <xf numFmtId="0" fontId="25" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1779,34 +1697,16 @@
     <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="16" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="35" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="5" borderId="42" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1"/>
@@ -1824,11 +1724,115 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="40" fillId="16" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="16" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="42" fillId="3" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="43" fillId="3" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="40" fillId="3" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="42" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="43" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="44" fillId="16" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="28" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="29" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="34" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="16" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
@@ -1836,20 +1840,16 @@
       <alignment horizontal="left" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="3" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="43" fillId="3" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="40" fillId="3" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="40" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="35" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="35" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="43" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="44" fillId="16" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="35" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
@@ -2239,13 +2239,13 @@
                   <c:v>0.05</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.05</c:v>
+                  <c:v>0.1</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>0.08</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>7.0000000000000007E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0</c:v>
@@ -3499,12 +3499,12 @@
   <sheetData>
     <row r="1" spans="1:16" ht="33.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="87"/>
-      <c r="B1" s="102" t="s">
+      <c r="B1" s="156" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
+      <c r="C1" s="156"/>
+      <c r="D1" s="156"/>
+      <c r="E1" s="156"/>
       <c r="F1" s="89"/>
       <c r="G1" s="89"/>
       <c r="H1" s="88"/>
@@ -3597,10 +3597,10 @@
         <v>0</v>
       </c>
       <c r="D6" s="17"/>
-      <c r="E6" s="103" t="s">
+      <c r="E6" s="157" t="s">
         <v>1</v>
       </c>
-      <c r="F6" s="103"/>
+      <c r="F6" s="157"/>
       <c r="G6" s="13"/>
       <c r="H6" s="1"/>
       <c r="I6" s="8"/>
@@ -3613,10 +3613,10 @@
     </row>
     <row r="7" spans="1:16" ht="20.399999999999999" x14ac:dyDescent="0.45">
       <c r="A7" s="10"/>
-      <c r="B7" s="104" t="s">
+      <c r="B7" s="158" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="105"/>
+      <c r="C7" s="159"/>
       <c r="D7" s="18" t="s">
         <v>3</v>
       </c>
@@ -3955,10 +3955,10 @@
         <v>6</v>
       </c>
       <c r="D20" s="45"/>
-      <c r="E20" s="106" t="s">
+      <c r="E20" s="160" t="s">
         <v>1</v>
       </c>
-      <c r="F20" s="106"/>
+      <c r="F20" s="160"/>
       <c r="G20" s="13"/>
       <c r="H20" s="1"/>
       <c r="I20" s="8"/>
@@ -3972,10 +3972,10 @@
     </row>
     <row r="21" spans="1:16" ht="20.399999999999999" x14ac:dyDescent="0.45">
       <c r="A21" s="10"/>
-      <c r="B21" s="107" t="s">
+      <c r="B21" s="161" t="s">
         <v>2</v>
       </c>
-      <c r="C21" s="108"/>
+      <c r="C21" s="162"/>
       <c r="D21" s="46" t="s">
         <v>3</v>
       </c>
@@ -4095,11 +4095,11 @@
         <v>0.05</v>
       </c>
       <c r="E25" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" s="49">
         <f t="shared" si="1"/>
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="G25" s="13"/>
       <c r="H25" s="1"/>
@@ -4123,10 +4123,12 @@
       <c r="D26" s="26">
         <v>0.08</v>
       </c>
-      <c r="E26" s="27"/>
+      <c r="E26" s="27">
+        <v>1</v>
+      </c>
       <c r="F26" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="G26" s="13"/>
       <c r="H26" s="1"/>
@@ -4150,10 +4152,12 @@
       <c r="D27" s="26">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="E27" s="27"/>
+      <c r="E27" s="27">
+        <v>1</v>
+      </c>
       <c r="F27" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G27" s="13"/>
       <c r="H27" s="1"/>
@@ -4175,7 +4179,9 @@
       <c r="D28" s="26">
         <v>0</v>
       </c>
-      <c r="E28" s="27"/>
+      <c r="E28" s="27">
+        <v>1</v>
+      </c>
       <c r="F28" s="49">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -4275,7 +4281,7 @@
       <c r="E32" s="53"/>
       <c r="F32" s="54">
         <f>SUM(F22:F31)</f>
-        <v>0.4</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="G32" s="13"/>
       <c r="H32" s="1"/>
@@ -4317,7 +4323,7 @@
       <c r="E34" s="53"/>
       <c r="F34" s="54">
         <f>F18+F32</f>
-        <v>2.35</v>
+        <v>2.5500000000000003</v>
       </c>
       <c r="G34" s="13"/>
       <c r="H34" s="1"/>
@@ -4332,10 +4338,10 @@
     </row>
     <row r="35" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="55"/>
-      <c r="B35" s="97" t="s">
+      <c r="B35" s="163" t="s">
         <v>8</v>
       </c>
-      <c r="C35" s="98"/>
+      <c r="C35" s="164"/>
       <c r="D35" s="56"/>
       <c r="E35" s="57"/>
       <c r="F35" s="57"/>
@@ -4352,8 +4358,8 @@
     </row>
     <row r="36" spans="1:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="55"/>
-      <c r="B36" s="99"/>
-      <c r="C36" s="99"/>
+      <c r="B36" s="165"/>
+      <c r="C36" s="165"/>
       <c r="D36" s="56"/>
       <c r="E36" s="57"/>
       <c r="F36" s="57"/>
@@ -4370,8 +4376,8 @@
     </row>
     <row r="37" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="55"/>
-      <c r="B37" s="99"/>
-      <c r="C37" s="99"/>
+      <c r="B37" s="165"/>
+      <c r="C37" s="165"/>
       <c r="D37" s="56"/>
       <c r="E37" s="57"/>
       <c r="F37" s="57"/>
@@ -4388,8 +4394,8 @@
     </row>
     <row r="38" spans="1:16" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A38" s="55"/>
-      <c r="B38" s="99"/>
-      <c r="C38" s="99"/>
+      <c r="B38" s="165"/>
+      <c r="C38" s="165"/>
       <c r="D38" s="56"/>
       <c r="E38" s="57"/>
       <c r="F38" s="57"/>
@@ -4406,8 +4412,8 @@
     </row>
     <row r="39" spans="1:16" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="55"/>
-      <c r="B39" s="99"/>
-      <c r="C39" s="99"/>
+      <c r="B39" s="165"/>
+      <c r="C39" s="165"/>
       <c r="D39" s="56"/>
       <c r="E39" s="57"/>
       <c r="F39" s="57"/>
@@ -4424,8 +4430,8 @@
     </row>
     <row r="40" spans="1:16" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A40" s="55"/>
-      <c r="B40" s="99"/>
-      <c r="C40" s="99"/>
+      <c r="B40" s="165"/>
+      <c r="C40" s="165"/>
       <c r="D40" s="56"/>
       <c r="E40" s="57"/>
       <c r="F40" s="57"/>
@@ -4442,8 +4448,8 @@
     </row>
     <row r="41" spans="1:16" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="55"/>
-      <c r="B41" s="99"/>
-      <c r="C41" s="99"/>
+      <c r="B41" s="165"/>
+      <c r="C41" s="165"/>
       <c r="D41" s="56"/>
       <c r="E41" s="57"/>
       <c r="F41" s="57"/>
@@ -4460,8 +4466,8 @@
     </row>
     <row r="42" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="55"/>
-      <c r="B42" s="99"/>
-      <c r="C42" s="99"/>
+      <c r="B42" s="165"/>
+      <c r="C42" s="165"/>
       <c r="D42" s="56"/>
       <c r="E42" s="57"/>
       <c r="F42" s="57"/>
@@ -4478,8 +4484,8 @@
     </row>
     <row r="43" spans="1:16" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A43" s="55"/>
-      <c r="B43" s="99"/>
-      <c r="C43" s="99"/>
+      <c r="B43" s="165"/>
+      <c r="C43" s="165"/>
       <c r="D43" s="56"/>
       <c r="E43" s="57"/>
       <c r="F43" s="57"/>
@@ -4496,8 +4502,8 @@
     </row>
     <row r="44" spans="1:16" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A44" s="55"/>
-      <c r="B44" s="99"/>
-      <c r="C44" s="99"/>
+      <c r="B44" s="165"/>
+      <c r="C44" s="165"/>
       <c r="D44" s="56"/>
       <c r="E44" s="57"/>
       <c r="F44" s="57"/>
@@ -4514,8 +4520,8 @@
     </row>
     <row r="45" spans="1:16" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A45" s="55"/>
-      <c r="B45" s="99"/>
-      <c r="C45" s="99"/>
+      <c r="B45" s="165"/>
+      <c r="C45" s="165"/>
       <c r="D45" s="56"/>
       <c r="E45" s="57"/>
       <c r="F45" s="57"/>
@@ -4639,17 +4645,17 @@
       <c r="P51" s="4"/>
     </row>
     <row r="52" spans="1:16" ht="28.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="100" t="s">
+      <c r="A52" s="154" t="s">
         <v>9</v>
       </c>
-      <c r="B52" s="100"/>
-      <c r="C52" s="100"/>
-      <c r="D52" s="100"/>
-      <c r="E52" s="100"/>
-      <c r="F52" s="100"/>
-      <c r="G52" s="100"/>
-      <c r="H52" s="100"/>
-      <c r="I52" s="101"/>
+      <c r="B52" s="154"/>
+      <c r="C52" s="154"/>
+      <c r="D52" s="154"/>
+      <c r="E52" s="154"/>
+      <c r="F52" s="154"/>
+      <c r="G52" s="154"/>
+      <c r="H52" s="154"/>
+      <c r="I52" s="155"/>
       <c r="J52" s="4"/>
       <c r="K52" s="4"/>
       <c r="L52" s="9"/>
@@ -5237,14 +5243,14 @@
   <sheetData>
     <row r="1" spans="1:18" ht="33.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="87"/>
-      <c r="B1" s="102" t="s">
+      <c r="B1" s="156" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
+      <c r="C1" s="156"/>
+      <c r="D1" s="156"/>
+      <c r="E1" s="156"/>
+      <c r="F1" s="156"/>
+      <c r="G1" s="156"/>
       <c r="H1" s="89"/>
       <c r="I1" s="89"/>
       <c r="J1" s="88"/>
@@ -5344,13 +5350,13 @@
       <c r="C6" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="109" t="s">
+      <c r="D6" s="171" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="109"/>
-      <c r="F6" s="109"/>
-      <c r="G6" s="109"/>
-      <c r="H6" s="109"/>
+      <c r="E6" s="171"/>
+      <c r="F6" s="171"/>
+      <c r="G6" s="171"/>
+      <c r="H6" s="171"/>
       <c r="I6" s="13"/>
       <c r="J6" s="1"/>
       <c r="K6" s="8"/>
@@ -5363,10 +5369,10 @@
     </row>
     <row r="7" spans="1:18" ht="20.399999999999999" x14ac:dyDescent="0.45">
       <c r="A7" s="10"/>
-      <c r="B7" s="104" t="s">
+      <c r="B7" s="158" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="105"/>
+      <c r="C7" s="159"/>
       <c r="D7" s="18" t="s">
         <v>41</v>
       </c>
@@ -5400,13 +5406,13 @@
       <c r="C8" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="D8" s="110" t="s">
+      <c r="D8" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="E8" s="110"/>
-      <c r="F8" s="110"/>
-      <c r="G8" s="110"/>
-      <c r="H8" s="110"/>
+      <c r="E8" s="97"/>
+      <c r="F8" s="97"/>
+      <c r="G8" s="97"/>
+      <c r="H8" s="97"/>
       <c r="I8" s="13"/>
       <c r="J8" s="1"/>
       <c r="K8" s="8"/>
@@ -5425,13 +5431,13 @@
       <c r="C9" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="D9" s="111" t="s">
+      <c r="D9" s="98" t="s">
         <v>46</v>
       </c>
-      <c r="E9" s="111"/>
-      <c r="F9" s="111"/>
-      <c r="G9" s="111"/>
-      <c r="H9" s="111"/>
+      <c r="E9" s="98"/>
+      <c r="F9" s="98"/>
+      <c r="G9" s="98"/>
+      <c r="H9" s="98"/>
       <c r="I9" s="13"/>
       <c r="J9" s="1"/>
       <c r="K9" s="8"/>
@@ -5450,11 +5456,11 @@
       <c r="C10" s="25" t="s">
         <v>83</v>
       </c>
-      <c r="D10" s="111"/>
-      <c r="E10" s="111"/>
-      <c r="F10" s="111"/>
-      <c r="G10" s="111"/>
-      <c r="H10" s="111" t="s">
+      <c r="D10" s="98"/>
+      <c r="E10" s="98"/>
+      <c r="F10" s="98"/>
+      <c r="G10" s="98"/>
+      <c r="H10" s="98" t="s">
         <v>46</v>
       </c>
       <c r="I10" s="13"/>
@@ -5474,11 +5480,11 @@
         <v>4</v>
       </c>
       <c r="C11" s="25"/>
-      <c r="D11" s="111"/>
-      <c r="E11" s="111"/>
-      <c r="F11" s="111"/>
-      <c r="G11" s="111"/>
-      <c r="H11" s="111"/>
+      <c r="D11" s="98"/>
+      <c r="E11" s="98"/>
+      <c r="F11" s="98"/>
+      <c r="G11" s="98"/>
+      <c r="H11" s="98"/>
       <c r="I11" s="13"/>
       <c r="J11" s="1"/>
       <c r="K11" s="8"/>
@@ -5496,11 +5502,11 @@
         <v>5</v>
       </c>
       <c r="C12" s="25"/>
-      <c r="D12" s="111"/>
-      <c r="E12" s="111"/>
-      <c r="F12" s="111"/>
-      <c r="G12" s="111"/>
-      <c r="H12" s="111"/>
+      <c r="D12" s="98"/>
+      <c r="E12" s="98"/>
+      <c r="F12" s="98"/>
+      <c r="G12" s="98"/>
+      <c r="H12" s="98"/>
       <c r="I12" s="13"/>
       <c r="J12" s="1"/>
       <c r="K12" s="8"/>
@@ -5518,11 +5524,11 @@
         <v>6</v>
       </c>
       <c r="C13" s="25"/>
-      <c r="D13" s="111"/>
-      <c r="E13" s="111"/>
-      <c r="F13" s="111"/>
-      <c r="G13" s="111"/>
-      <c r="H13" s="111"/>
+      <c r="D13" s="98"/>
+      <c r="E13" s="98"/>
+      <c r="F13" s="98"/>
+      <c r="G13" s="98"/>
+      <c r="H13" s="98"/>
       <c r="I13" s="13"/>
       <c r="J13" s="1"/>
       <c r="K13" s="8"/>
@@ -5540,11 +5546,11 @@
         <v>7</v>
       </c>
       <c r="C14" s="25"/>
-      <c r="D14" s="111"/>
-      <c r="E14" s="111"/>
-      <c r="F14" s="111"/>
-      <c r="G14" s="111"/>
-      <c r="H14" s="111"/>
+      <c r="D14" s="98"/>
+      <c r="E14" s="98"/>
+      <c r="F14" s="98"/>
+      <c r="G14" s="98"/>
+      <c r="H14" s="98"/>
       <c r="I14" s="13"/>
       <c r="J14" s="1"/>
       <c r="K14" s="8"/>
@@ -5562,11 +5568,11 @@
         <v>8</v>
       </c>
       <c r="C15" s="25"/>
-      <c r="D15" s="111"/>
-      <c r="E15" s="111"/>
-      <c r="F15" s="111"/>
-      <c r="G15" s="111"/>
-      <c r="H15" s="111"/>
+      <c r="D15" s="98"/>
+      <c r="E15" s="98"/>
+      <c r="F15" s="98"/>
+      <c r="G15" s="98"/>
+      <c r="H15" s="98"/>
       <c r="I15" s="13"/>
       <c r="J15" s="1"/>
       <c r="K15" s="8"/>
@@ -5584,11 +5590,11 @@
         <v>9</v>
       </c>
       <c r="C16" s="25"/>
-      <c r="D16" s="111"/>
-      <c r="E16" s="111"/>
-      <c r="F16" s="111"/>
-      <c r="G16" s="111"/>
-      <c r="H16" s="111"/>
+      <c r="D16" s="98"/>
+      <c r="E16" s="98"/>
+      <c r="F16" s="98"/>
+      <c r="G16" s="98"/>
+      <c r="H16" s="98"/>
       <c r="I16" s="13"/>
       <c r="J16" s="1"/>
       <c r="K16" s="8"/>
@@ -5606,11 +5612,11 @@
         <v>10</v>
       </c>
       <c r="C17" s="28"/>
-      <c r="D17" s="112"/>
-      <c r="E17" s="112"/>
-      <c r="F17" s="112"/>
-      <c r="G17" s="112"/>
-      <c r="H17" s="112"/>
+      <c r="D17" s="99"/>
+      <c r="E17" s="99"/>
+      <c r="F17" s="99"/>
+      <c r="G17" s="99"/>
+      <c r="H17" s="99"/>
       <c r="I17" s="13"/>
       <c r="J17" s="1"/>
       <c r="K17" s="8"/>
@@ -5624,13 +5630,13 @@
     </row>
     <row r="18" spans="1:18" ht="5.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="31"/>
-      <c r="B18" s="113"/>
-      <c r="C18" s="114"/>
-      <c r="D18" s="114"/>
-      <c r="E18" s="114"/>
-      <c r="F18" s="114"/>
-      <c r="G18" s="114"/>
-      <c r="H18" s="115"/>
+      <c r="B18" s="172"/>
+      <c r="C18" s="173"/>
+      <c r="D18" s="173"/>
+      <c r="E18" s="173"/>
+      <c r="F18" s="173"/>
+      <c r="G18" s="173"/>
+      <c r="H18" s="174"/>
       <c r="I18" s="37"/>
       <c r="J18" s="38"/>
       <c r="K18" s="39"/>
@@ -5668,13 +5674,13 @@
       <c r="C20" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="D20" s="116" t="s">
+      <c r="D20" s="175" t="s">
         <v>1</v>
       </c>
-      <c r="E20" s="116"/>
-      <c r="F20" s="116"/>
-      <c r="G20" s="116"/>
-      <c r="H20" s="116"/>
+      <c r="E20" s="175"/>
+      <c r="F20" s="175"/>
+      <c r="G20" s="175"/>
+      <c r="H20" s="175"/>
       <c r="I20" s="13"/>
       <c r="J20" s="1"/>
       <c r="K20" s="8"/>
@@ -5688,17 +5694,17 @@
     </row>
     <row r="21" spans="1:18" ht="20.399999999999999" x14ac:dyDescent="0.45">
       <c r="A21" s="10"/>
-      <c r="B21" s="107" t="s">
+      <c r="B21" s="161" t="s">
         <v>40</v>
       </c>
-      <c r="C21" s="108"/>
+      <c r="C21" s="162"/>
       <c r="D21" s="46" t="s">
         <v>41</v>
       </c>
       <c r="E21" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="F21" s="117" t="s">
+      <c r="F21" s="100" t="s">
         <v>43</v>
       </c>
       <c r="G21" s="47" t="s">
@@ -5726,13 +5732,13 @@
       <c r="C22" s="92" t="s">
         <v>50</v>
       </c>
-      <c r="D22" s="110"/>
-      <c r="E22" s="110" t="s">
+      <c r="D22" s="97"/>
+      <c r="E22" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="F22" s="110"/>
-      <c r="G22" s="110"/>
-      <c r="H22" s="110"/>
+      <c r="F22" s="97"/>
+      <c r="G22" s="97"/>
+      <c r="H22" s="97"/>
       <c r="I22" s="13"/>
       <c r="J22" s="1"/>
       <c r="K22" s="8"/>
@@ -5752,13 +5758,13 @@
       <c r="C23" s="94" t="s">
         <v>51</v>
       </c>
-      <c r="D23" s="111"/>
-      <c r="E23" s="111"/>
-      <c r="F23" s="111"/>
-      <c r="G23" s="111" t="s">
+      <c r="D23" s="98"/>
+      <c r="E23" s="98"/>
+      <c r="F23" s="98"/>
+      <c r="G23" s="98" t="s">
         <v>46</v>
       </c>
-      <c r="H23" s="111"/>
+      <c r="H23" s="98"/>
       <c r="I23" s="13"/>
       <c r="J23" s="1"/>
       <c r="K23" s="8"/>
@@ -5776,11 +5782,11 @@
         <v>3</v>
       </c>
       <c r="C24" s="94"/>
-      <c r="D24" s="111"/>
-      <c r="E24" s="111"/>
-      <c r="F24" s="111"/>
-      <c r="G24" s="111"/>
-      <c r="H24" s="111"/>
+      <c r="D24" s="98"/>
+      <c r="E24" s="98"/>
+      <c r="F24" s="98"/>
+      <c r="G24" s="98"/>
+      <c r="H24" s="98"/>
       <c r="I24" s="13"/>
       <c r="J24" s="1"/>
       <c r="K24" s="8"/>
@@ -5798,11 +5804,11 @@
         <v>4</v>
       </c>
       <c r="C25" s="94"/>
-      <c r="D25" s="111"/>
-      <c r="E25" s="111"/>
-      <c r="F25" s="111"/>
-      <c r="G25" s="111"/>
-      <c r="H25" s="111"/>
+      <c r="D25" s="98"/>
+      <c r="E25" s="98"/>
+      <c r="F25" s="98"/>
+      <c r="G25" s="98"/>
+      <c r="H25" s="98"/>
       <c r="I25" s="13"/>
       <c r="J25" s="1"/>
       <c r="K25" s="8"/>
@@ -5820,11 +5826,11 @@
         <v>5</v>
       </c>
       <c r="C26" s="94"/>
-      <c r="D26" s="111"/>
-      <c r="E26" s="111"/>
-      <c r="F26" s="111"/>
-      <c r="G26" s="111"/>
-      <c r="H26" s="111"/>
+      <c r="D26" s="98"/>
+      <c r="E26" s="98"/>
+      <c r="F26" s="98"/>
+      <c r="G26" s="98"/>
+      <c r="H26" s="98"/>
       <c r="I26" s="13"/>
       <c r="J26" s="1"/>
       <c r="K26" s="8"/>
@@ -5842,11 +5848,11 @@
         <v>6</v>
       </c>
       <c r="C27" s="94"/>
-      <c r="D27" s="111"/>
-      <c r="E27" s="111"/>
-      <c r="F27" s="111"/>
-      <c r="G27" s="111"/>
-      <c r="H27" s="111"/>
+      <c r="D27" s="98"/>
+      <c r="E27" s="98"/>
+      <c r="F27" s="98"/>
+      <c r="G27" s="98"/>
+      <c r="H27" s="98"/>
       <c r="I27" s="13"/>
       <c r="J27" s="1"/>
       <c r="K27" s="8"/>
@@ -5864,11 +5870,11 @@
         <v>7</v>
       </c>
       <c r="C28" s="94"/>
-      <c r="D28" s="111"/>
-      <c r="E28" s="111"/>
-      <c r="F28" s="111"/>
-      <c r="G28" s="111"/>
-      <c r="H28" s="111"/>
+      <c r="D28" s="98"/>
+      <c r="E28" s="98"/>
+      <c r="F28" s="98"/>
+      <c r="G28" s="98"/>
+      <c r="H28" s="98"/>
       <c r="I28" s="13"/>
       <c r="J28" s="1"/>
       <c r="K28" s="8"/>
@@ -5885,11 +5891,11 @@
         <v>8</v>
       </c>
       <c r="C29" s="94"/>
-      <c r="D29" s="111"/>
-      <c r="E29" s="111"/>
-      <c r="F29" s="111"/>
-      <c r="G29" s="111"/>
-      <c r="H29" s="111"/>
+      <c r="D29" s="98"/>
+      <c r="E29" s="98"/>
+      <c r="F29" s="98"/>
+      <c r="G29" s="98"/>
+      <c r="H29" s="98"/>
       <c r="I29" s="13"/>
       <c r="J29" s="1"/>
       <c r="K29" s="8"/>
@@ -5906,11 +5912,11 @@
         <v>9</v>
       </c>
       <c r="C30" s="94"/>
-      <c r="D30" s="111"/>
-      <c r="E30" s="111"/>
-      <c r="F30" s="111"/>
-      <c r="G30" s="111"/>
-      <c r="H30" s="111"/>
+      <c r="D30" s="98"/>
+      <c r="E30" s="98"/>
+      <c r="F30" s="98"/>
+      <c r="G30" s="98"/>
+      <c r="H30" s="98"/>
       <c r="I30" s="13"/>
       <c r="J30" s="1"/>
       <c r="K30" s="8"/>
@@ -5927,11 +5933,11 @@
         <v>10</v>
       </c>
       <c r="C31" s="95"/>
-      <c r="D31" s="112"/>
-      <c r="E31" s="112"/>
-      <c r="F31" s="112"/>
-      <c r="G31" s="112"/>
-      <c r="H31" s="112"/>
+      <c r="D31" s="99"/>
+      <c r="E31" s="99"/>
+      <c r="F31" s="99"/>
+      <c r="G31" s="99"/>
+      <c r="H31" s="99"/>
       <c r="I31" s="13"/>
       <c r="J31" s="1"/>
       <c r="K31" s="8"/>
@@ -5944,13 +5950,13 @@
       <c r="R31" s="4"/>
     </row>
     <row r="32" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="118"/>
-      <c r="C32" s="119"/>
-      <c r="D32" s="119"/>
-      <c r="E32" s="119"/>
-      <c r="F32" s="119"/>
-      <c r="G32" s="119"/>
-      <c r="H32" s="120"/>
+      <c r="B32" s="166"/>
+      <c r="C32" s="167"/>
+      <c r="D32" s="167"/>
+      <c r="E32" s="167"/>
+      <c r="F32" s="167"/>
+      <c r="G32" s="167"/>
+      <c r="H32" s="168"/>
       <c r="I32" s="13"/>
       <c r="J32" s="1"/>
       <c r="K32" s="8"/>
@@ -5963,14 +5969,14 @@
       <c r="R32" s="4"/>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A33" s="121"/>
-      <c r="B33" s="121"/>
-      <c r="C33" s="121"/>
-      <c r="D33" s="121"/>
-      <c r="E33" s="121"/>
-      <c r="F33" s="121"/>
-      <c r="G33" s="121"/>
-      <c r="H33" s="121"/>
+      <c r="A33" s="101"/>
+      <c r="B33" s="101"/>
+      <c r="C33" s="101"/>
+      <c r="D33" s="101"/>
+      <c r="E33" s="101"/>
+      <c r="F33" s="101"/>
+      <c r="G33" s="101"/>
+      <c r="H33" s="101"/>
       <c r="I33" s="13"/>
       <c r="J33" s="63"/>
       <c r="K33" s="64"/>
@@ -5988,13 +5994,13 @@
       <c r="C34" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="D34" s="109" t="s">
+      <c r="D34" s="171" t="s">
         <v>1</v>
       </c>
-      <c r="E34" s="109"/>
-      <c r="F34" s="109"/>
-      <c r="G34" s="109"/>
-      <c r="H34" s="109"/>
+      <c r="E34" s="171"/>
+      <c r="F34" s="171"/>
+      <c r="G34" s="171"/>
+      <c r="H34" s="171"/>
       <c r="I34" s="13"/>
       <c r="J34" s="1"/>
       <c r="K34" s="8"/>
@@ -6007,10 +6013,10 @@
     </row>
     <row r="35" spans="1:18" ht="20.399999999999999" x14ac:dyDescent="0.45">
       <c r="A35" s="10"/>
-      <c r="B35" s="104" t="s">
+      <c r="B35" s="158" t="s">
         <v>40</v>
       </c>
-      <c r="C35" s="105"/>
+      <c r="C35" s="159"/>
       <c r="D35" s="18" t="s">
         <v>41</v>
       </c>
@@ -6044,11 +6050,11 @@
       <c r="C36" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="D36" s="110"/>
-      <c r="E36" s="110"/>
-      <c r="F36" s="110"/>
-      <c r="G36" s="110"/>
-      <c r="H36" s="110" t="s">
+      <c r="D36" s="97"/>
+      <c r="E36" s="97"/>
+      <c r="F36" s="97"/>
+      <c r="G36" s="97"/>
+      <c r="H36" s="97" t="s">
         <v>46</v>
       </c>
       <c r="I36" s="13"/>
@@ -6069,13 +6075,13 @@
       <c r="C37" s="25" t="s">
         <v>86</v>
       </c>
-      <c r="D37" s="111"/>
-      <c r="E37" s="111"/>
-      <c r="F37" s="111"/>
-      <c r="G37" s="111" t="s">
+      <c r="D37" s="98"/>
+      <c r="E37" s="98"/>
+      <c r="F37" s="98"/>
+      <c r="G37" s="98" t="s">
         <v>46</v>
       </c>
-      <c r="H37" s="111"/>
+      <c r="H37" s="98"/>
       <c r="I37" s="13"/>
       <c r="J37" s="1"/>
       <c r="K37" s="8"/>
@@ -6094,11 +6100,11 @@
       <c r="C38" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="D38" s="111"/>
-      <c r="E38" s="111"/>
-      <c r="F38" s="111"/>
-      <c r="G38" s="111"/>
-      <c r="H38" s="111" t="s">
+      <c r="D38" s="98"/>
+      <c r="E38" s="98"/>
+      <c r="F38" s="98"/>
+      <c r="G38" s="98"/>
+      <c r="H38" s="98" t="s">
         <v>46</v>
       </c>
       <c r="I38" s="13"/>
@@ -6120,13 +6126,13 @@
       <c r="C39" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="D39" s="111"/>
-      <c r="E39" s="111" t="s">
+      <c r="D39" s="98"/>
+      <c r="E39" s="98" t="s">
         <v>46</v>
       </c>
-      <c r="F39" s="111"/>
-      <c r="G39" s="111"/>
-      <c r="H39" s="111"/>
+      <c r="F39" s="98"/>
+      <c r="G39" s="98"/>
+      <c r="H39" s="98"/>
       <c r="I39" s="13"/>
       <c r="J39" s="1"/>
       <c r="K39" s="8"/>
@@ -6146,13 +6152,13 @@
       <c r="C40" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="D40" s="111" t="s">
+      <c r="D40" s="98" t="s">
         <v>46</v>
       </c>
-      <c r="E40" s="111"/>
-      <c r="F40" s="111"/>
-      <c r="G40" s="111"/>
-      <c r="H40" s="111"/>
+      <c r="E40" s="98"/>
+      <c r="F40" s="98"/>
+      <c r="G40" s="98"/>
+      <c r="H40" s="98"/>
       <c r="I40" s="13"/>
       <c r="J40" s="1"/>
       <c r="K40" s="8"/>
@@ -6170,11 +6176,11 @@
         <v>6</v>
       </c>
       <c r="C41" s="25"/>
-      <c r="D41" s="111"/>
-      <c r="E41" s="111"/>
-      <c r="F41" s="111"/>
-      <c r="G41" s="111"/>
-      <c r="H41" s="111"/>
+      <c r="D41" s="98"/>
+      <c r="E41" s="98"/>
+      <c r="F41" s="98"/>
+      <c r="G41" s="98"/>
+      <c r="H41" s="98"/>
       <c r="I41" s="13"/>
       <c r="J41" s="1"/>
       <c r="K41" s="8"/>
@@ -6192,11 +6198,11 @@
         <v>7</v>
       </c>
       <c r="C42" s="25"/>
-      <c r="D42" s="111"/>
-      <c r="E42" s="111"/>
-      <c r="F42" s="111"/>
-      <c r="G42" s="111"/>
-      <c r="H42" s="111"/>
+      <c r="D42" s="98"/>
+      <c r="E42" s="98"/>
+      <c r="F42" s="98"/>
+      <c r="G42" s="98"/>
+      <c r="H42" s="98"/>
       <c r="I42" s="13"/>
       <c r="J42" s="1"/>
       <c r="K42" s="8"/>
@@ -6214,11 +6220,11 @@
         <v>8</v>
       </c>
       <c r="C43" s="25"/>
-      <c r="D43" s="111"/>
-      <c r="E43" s="111"/>
-      <c r="F43" s="111"/>
-      <c r="G43" s="111"/>
-      <c r="H43" s="111"/>
+      <c r="D43" s="98"/>
+      <c r="E43" s="98"/>
+      <c r="F43" s="98"/>
+      <c r="G43" s="98"/>
+      <c r="H43" s="98"/>
       <c r="I43" s="13"/>
       <c r="J43" s="1"/>
       <c r="K43" s="8"/>
@@ -6236,11 +6242,11 @@
         <v>9</v>
       </c>
       <c r="C44" s="25"/>
-      <c r="D44" s="111"/>
-      <c r="E44" s="111"/>
-      <c r="F44" s="111"/>
-      <c r="G44" s="111"/>
-      <c r="H44" s="111"/>
+      <c r="D44" s="98"/>
+      <c r="E44" s="98"/>
+      <c r="F44" s="98"/>
+      <c r="G44" s="98"/>
+      <c r="H44" s="98"/>
       <c r="I44" s="13"/>
       <c r="J44" s="1"/>
       <c r="K44" s="8"/>
@@ -6258,11 +6264,11 @@
         <v>10</v>
       </c>
       <c r="C45" s="28"/>
-      <c r="D45" s="112"/>
-      <c r="E45" s="112"/>
-      <c r="F45" s="112"/>
-      <c r="G45" s="112"/>
-      <c r="H45" s="112"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
+      <c r="F45" s="99"/>
+      <c r="G45" s="99"/>
+      <c r="H45" s="99"/>
       <c r="I45" s="13"/>
       <c r="J45" s="1"/>
       <c r="K45" s="8"/>
@@ -6276,13 +6282,13 @@
     </row>
     <row r="46" spans="1:18" ht="5.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="31"/>
-      <c r="B46" s="113"/>
-      <c r="C46" s="114"/>
-      <c r="D46" s="114"/>
-      <c r="E46" s="114"/>
-      <c r="F46" s="114"/>
-      <c r="G46" s="114"/>
-      <c r="H46" s="115"/>
+      <c r="B46" s="172"/>
+      <c r="C46" s="173"/>
+      <c r="D46" s="173"/>
+      <c r="E46" s="173"/>
+      <c r="F46" s="173"/>
+      <c r="G46" s="173"/>
+      <c r="H46" s="174"/>
       <c r="I46" s="37"/>
       <c r="J46" s="38"/>
       <c r="K46" s="39"/>
@@ -6295,14 +6301,14 @@
       <c r="R46" s="4"/>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A47" s="121"/>
-      <c r="B47" s="121"/>
-      <c r="C47" s="121"/>
-      <c r="D47" s="121"/>
-      <c r="E47" s="121"/>
-      <c r="F47" s="121"/>
-      <c r="G47" s="121"/>
-      <c r="H47" s="121"/>
+      <c r="A47" s="101"/>
+      <c r="B47" s="101"/>
+      <c r="C47" s="101"/>
+      <c r="D47" s="101"/>
+      <c r="E47" s="101"/>
+      <c r="F47" s="101"/>
+      <c r="G47" s="101"/>
+      <c r="H47" s="101"/>
       <c r="I47" s="13"/>
       <c r="J47" s="63"/>
       <c r="K47" s="64"/>
@@ -6320,13 +6326,13 @@
       <c r="C48" s="44" t="s">
         <v>54</v>
       </c>
-      <c r="D48" s="116" t="s">
+      <c r="D48" s="175" t="s">
         <v>1</v>
       </c>
-      <c r="E48" s="116"/>
-      <c r="F48" s="116"/>
-      <c r="G48" s="116"/>
-      <c r="H48" s="116"/>
+      <c r="E48" s="175"/>
+      <c r="F48" s="175"/>
+      <c r="G48" s="175"/>
+      <c r="H48" s="175"/>
       <c r="I48" s="13"/>
       <c r="J48" s="1"/>
       <c r="K48" s="8"/>
@@ -6340,17 +6346,17 @@
     </row>
     <row r="49" spans="1:18" ht="20.399999999999999" x14ac:dyDescent="0.45">
       <c r="A49" s="10"/>
-      <c r="B49" s="107" t="s">
+      <c r="B49" s="161" t="s">
         <v>40</v>
       </c>
-      <c r="C49" s="108"/>
+      <c r="C49" s="162"/>
       <c r="D49" s="46" t="s">
         <v>41</v>
       </c>
       <c r="E49" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="F49" s="117" t="s">
+      <c r="F49" s="100" t="s">
         <v>43</v>
       </c>
       <c r="G49" s="47" t="s">
@@ -6378,11 +6384,11 @@
       <c r="C50" s="92" t="s">
         <v>55</v>
       </c>
-      <c r="D50" s="110"/>
-      <c r="E50" s="110"/>
-      <c r="F50" s="110"/>
-      <c r="G50" s="110"/>
-      <c r="H50" s="110" t="s">
+      <c r="D50" s="97"/>
+      <c r="E50" s="97"/>
+      <c r="F50" s="97"/>
+      <c r="G50" s="97"/>
+      <c r="H50" s="97" t="s">
         <v>46</v>
       </c>
       <c r="I50" s="13"/>
@@ -6404,11 +6410,11 @@
       <c r="C51" s="93" t="s">
         <v>56</v>
       </c>
-      <c r="D51" s="111"/>
-      <c r="E51" s="111"/>
-      <c r="F51" s="111"/>
-      <c r="G51" s="111"/>
-      <c r="H51" s="111" t="s">
+      <c r="D51" s="98"/>
+      <c r="E51" s="98"/>
+      <c r="F51" s="98"/>
+      <c r="G51" s="98"/>
+      <c r="H51" s="98" t="s">
         <v>46</v>
       </c>
       <c r="I51" s="13"/>
@@ -6430,13 +6436,13 @@
       <c r="C52" s="94" t="s">
         <v>57</v>
       </c>
-      <c r="D52" s="111"/>
-      <c r="E52" s="111" t="s">
+      <c r="D52" s="98"/>
+      <c r="E52" s="98" t="s">
         <v>46</v>
       </c>
-      <c r="F52" s="111"/>
-      <c r="G52" s="111"/>
-      <c r="H52" s="111"/>
+      <c r="F52" s="98"/>
+      <c r="G52" s="98"/>
+      <c r="H52" s="98"/>
       <c r="I52" s="13"/>
       <c r="J52" s="1"/>
       <c r="K52" s="8"/>
@@ -6456,13 +6462,13 @@
       <c r="C53" s="94" t="s">
         <v>58</v>
       </c>
-      <c r="D53" s="111"/>
-      <c r="E53" s="111" t="s">
+      <c r="D53" s="98"/>
+      <c r="E53" s="98" t="s">
         <v>46</v>
       </c>
-      <c r="F53" s="111"/>
-      <c r="G53" s="111"/>
-      <c r="H53" s="111"/>
+      <c r="F53" s="98"/>
+      <c r="G53" s="98"/>
+      <c r="H53" s="98"/>
       <c r="I53" s="13"/>
       <c r="J53" s="1"/>
       <c r="K53" s="8"/>
@@ -6482,13 +6488,13 @@
       <c r="C54" s="94" t="s">
         <v>71</v>
       </c>
-      <c r="D54" s="111"/>
-      <c r="E54" s="111" t="s">
+      <c r="D54" s="98"/>
+      <c r="E54" s="98" t="s">
         <v>46</v>
       </c>
-      <c r="F54" s="111"/>
-      <c r="G54" s="111"/>
-      <c r="H54" s="111"/>
+      <c r="F54" s="98"/>
+      <c r="G54" s="98"/>
+      <c r="H54" s="98"/>
       <c r="I54" s="13"/>
       <c r="J54" s="1"/>
       <c r="K54" s="8"/>
@@ -6506,11 +6512,11 @@
         <v>6</v>
       </c>
       <c r="C55" s="94"/>
-      <c r="D55" s="111"/>
-      <c r="E55" s="111"/>
-      <c r="F55" s="111"/>
-      <c r="G55" s="111"/>
-      <c r="H55" s="111"/>
+      <c r="D55" s="98"/>
+      <c r="E55" s="98"/>
+      <c r="F55" s="98"/>
+      <c r="G55" s="98"/>
+      <c r="H55" s="98"/>
       <c r="I55" s="13"/>
       <c r="J55" s="1"/>
       <c r="K55" s="8"/>
@@ -6528,11 +6534,11 @@
         <v>7</v>
       </c>
       <c r="C56" s="94"/>
-      <c r="D56" s="111"/>
-      <c r="E56" s="111"/>
-      <c r="F56" s="111"/>
-      <c r="G56" s="111"/>
-      <c r="H56" s="111"/>
+      <c r="D56" s="98"/>
+      <c r="E56" s="98"/>
+      <c r="F56" s="98"/>
+      <c r="G56" s="98"/>
+      <c r="H56" s="98"/>
       <c r="I56" s="13"/>
       <c r="J56" s="1"/>
       <c r="K56" s="8"/>
@@ -6549,11 +6555,11 @@
         <v>8</v>
       </c>
       <c r="C57" s="94"/>
-      <c r="D57" s="111"/>
-      <c r="E57" s="111"/>
-      <c r="F57" s="111"/>
-      <c r="G57" s="111"/>
-      <c r="H57" s="111"/>
+      <c r="D57" s="98"/>
+      <c r="E57" s="98"/>
+      <c r="F57" s="98"/>
+      <c r="G57" s="98"/>
+      <c r="H57" s="98"/>
       <c r="I57" s="13"/>
       <c r="J57" s="1"/>
       <c r="K57" s="8"/>
@@ -6570,11 +6576,11 @@
         <v>9</v>
       </c>
       <c r="C58" s="94"/>
-      <c r="D58" s="111"/>
-      <c r="E58" s="111"/>
-      <c r="F58" s="111"/>
-      <c r="G58" s="111"/>
-      <c r="H58" s="111"/>
+      <c r="D58" s="98"/>
+      <c r="E58" s="98"/>
+      <c r="F58" s="98"/>
+      <c r="G58" s="98"/>
+      <c r="H58" s="98"/>
       <c r="I58" s="13"/>
       <c r="J58" s="1"/>
       <c r="K58" s="8"/>
@@ -6591,11 +6597,11 @@
         <v>10</v>
       </c>
       <c r="C59" s="95"/>
-      <c r="D59" s="112"/>
-      <c r="E59" s="112"/>
-      <c r="F59" s="112"/>
-      <c r="G59" s="112"/>
-      <c r="H59" s="112"/>
+      <c r="D59" s="99"/>
+      <c r="E59" s="99"/>
+      <c r="F59" s="99"/>
+      <c r="G59" s="99"/>
+      <c r="H59" s="99"/>
       <c r="I59" s="13"/>
       <c r="J59" s="1"/>
       <c r="K59" s="8"/>
@@ -6608,13 +6614,13 @@
       <c r="R59" s="4"/>
     </row>
     <row r="60" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="118"/>
-      <c r="C60" s="119"/>
-      <c r="D60" s="119"/>
-      <c r="E60" s="119"/>
-      <c r="F60" s="119"/>
-      <c r="G60" s="119"/>
-      <c r="H60" s="120"/>
+      <c r="B60" s="166"/>
+      <c r="C60" s="167"/>
+      <c r="D60" s="167"/>
+      <c r="E60" s="167"/>
+      <c r="F60" s="167"/>
+      <c r="G60" s="167"/>
+      <c r="H60" s="168"/>
       <c r="I60" s="13"/>
       <c r="J60" s="1"/>
       <c r="K60" s="8"/>
@@ -6627,14 +6633,14 @@
       <c r="R60" s="4"/>
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A61" s="121"/>
-      <c r="B61" s="121"/>
-      <c r="C61" s="121"/>
-      <c r="D61" s="121"/>
-      <c r="E61" s="121"/>
-      <c r="F61" s="121"/>
-      <c r="G61" s="121"/>
-      <c r="H61" s="121"/>
+      <c r="A61" s="101"/>
+      <c r="B61" s="101"/>
+      <c r="C61" s="101"/>
+      <c r="D61" s="101"/>
+      <c r="E61" s="101"/>
+      <c r="F61" s="101"/>
+      <c r="G61" s="101"/>
+      <c r="H61" s="101"/>
       <c r="I61" s="13"/>
       <c r="J61" s="63"/>
       <c r="K61" s="64"/>
@@ -6767,19 +6773,19 @@
       <c r="R67" s="4"/>
     </row>
     <row r="68" spans="1:18" ht="28.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="100" t="s">
+      <c r="A68" s="154" t="s">
         <v>9</v>
       </c>
-      <c r="B68" s="100"/>
-      <c r="C68" s="100"/>
-      <c r="D68" s="100"/>
-      <c r="E68" s="100"/>
-      <c r="F68" s="100"/>
-      <c r="G68" s="100"/>
-      <c r="H68" s="100"/>
-      <c r="I68" s="100"/>
-      <c r="J68" s="100"/>
-      <c r="K68" s="101"/>
+      <c r="B68" s="154"/>
+      <c r="C68" s="154"/>
+      <c r="D68" s="154"/>
+      <c r="E68" s="154"/>
+      <c r="F68" s="154"/>
+      <c r="G68" s="154"/>
+      <c r="H68" s="154"/>
+      <c r="I68" s="154"/>
+      <c r="J68" s="154"/>
+      <c r="K68" s="155"/>
       <c r="L68" s="4"/>
       <c r="M68" s="4"/>
       <c r="N68" s="9"/>
@@ -6810,15 +6816,15 @@
     </row>
     <row r="70" spans="1:18" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="67"/>
-      <c r="B70" s="122" t="s">
+      <c r="B70" s="169" t="s">
         <v>59</v>
       </c>
-      <c r="C70" s="122"/>
-      <c r="D70" s="122"/>
-      <c r="E70" s="122"/>
-      <c r="F70" s="122"/>
-      <c r="G70" s="122"/>
-      <c r="H70" s="122"/>
+      <c r="C70" s="169"/>
+      <c r="D70" s="169"/>
+      <c r="E70" s="169"/>
+      <c r="F70" s="169"/>
+      <c r="G70" s="169"/>
+      <c r="H70" s="169"/>
       <c r="I70" s="68"/>
       <c r="J70" s="67"/>
       <c r="K70" s="69"/>
@@ -6832,13 +6838,13 @@
     </row>
     <row r="71" spans="1:18" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="67"/>
-      <c r="B71" s="122"/>
-      <c r="C71" s="122"/>
-      <c r="D71" s="122"/>
-      <c r="E71" s="122"/>
-      <c r="F71" s="122"/>
-      <c r="G71" s="122"/>
-      <c r="H71" s="122"/>
+      <c r="B71" s="169"/>
+      <c r="C71" s="169"/>
+      <c r="D71" s="169"/>
+      <c r="E71" s="169"/>
+      <c r="F71" s="169"/>
+      <c r="G71" s="169"/>
+      <c r="H71" s="169"/>
       <c r="I71" s="68"/>
       <c r="J71" s="67"/>
       <c r="K71" s="69"/>
@@ -6852,13 +6858,13 @@
     </row>
     <row r="72" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="67"/>
-      <c r="B72" s="123"/>
-      <c r="C72" s="123"/>
-      <c r="D72" s="123"/>
-      <c r="E72" s="123"/>
-      <c r="F72" s="123"/>
-      <c r="G72" s="123"/>
-      <c r="H72" s="123"/>
+      <c r="B72" s="102"/>
+      <c r="C72" s="102"/>
+      <c r="D72" s="102"/>
+      <c r="E72" s="102"/>
+      <c r="F72" s="102"/>
+      <c r="G72" s="102"/>
+      <c r="H72" s="102"/>
       <c r="I72" s="68"/>
       <c r="J72" s="67"/>
       <c r="K72" s="69"/>
@@ -6872,15 +6878,15 @@
     </row>
     <row r="73" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="67"/>
-      <c r="B73" s="124" t="s">
+      <c r="B73" s="170" t="s">
         <v>60</v>
       </c>
-      <c r="C73" s="124"/>
-      <c r="D73" s="124"/>
-      <c r="E73" s="124"/>
-      <c r="F73" s="124"/>
-      <c r="G73" s="124"/>
-      <c r="H73" s="124"/>
+      <c r="C73" s="170"/>
+      <c r="D73" s="170"/>
+      <c r="E73" s="170"/>
+      <c r="F73" s="170"/>
+      <c r="G73" s="170"/>
+      <c r="H73" s="170"/>
       <c r="I73" s="68"/>
       <c r="J73" s="67"/>
       <c r="K73" s="69"/>
@@ -6894,13 +6900,13 @@
     </row>
     <row r="74" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="67"/>
-      <c r="B74" s="124"/>
-      <c r="C74" s="124"/>
-      <c r="D74" s="124"/>
-      <c r="E74" s="124"/>
-      <c r="F74" s="124"/>
-      <c r="G74" s="124"/>
-      <c r="H74" s="124"/>
+      <c r="B74" s="170"/>
+      <c r="C74" s="170"/>
+      <c r="D74" s="170"/>
+      <c r="E74" s="170"/>
+      <c r="F74" s="170"/>
+      <c r="G74" s="170"/>
+      <c r="H74" s="170"/>
       <c r="I74" s="68"/>
       <c r="J74" s="67"/>
       <c r="K74" s="69"/>
@@ -6914,13 +6920,13 @@
     </row>
     <row r="75" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="67"/>
-      <c r="B75" s="124"/>
-      <c r="C75" s="124"/>
-      <c r="D75" s="124"/>
-      <c r="E75" s="124"/>
-      <c r="F75" s="124"/>
-      <c r="G75" s="124"/>
-      <c r="H75" s="124"/>
+      <c r="B75" s="170"/>
+      <c r="C75" s="170"/>
+      <c r="D75" s="170"/>
+      <c r="E75" s="170"/>
+      <c r="F75" s="170"/>
+      <c r="G75" s="170"/>
+      <c r="H75" s="170"/>
       <c r="I75" s="68"/>
       <c r="J75" s="67"/>
       <c r="K75" s="69"/>
@@ -6934,13 +6940,13 @@
     </row>
     <row r="76" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="67"/>
-      <c r="B76" s="124"/>
-      <c r="C76" s="124"/>
-      <c r="D76" s="124"/>
-      <c r="E76" s="124"/>
-      <c r="F76" s="124"/>
-      <c r="G76" s="124"/>
-      <c r="H76" s="124"/>
+      <c r="B76" s="170"/>
+      <c r="C76" s="170"/>
+      <c r="D76" s="170"/>
+      <c r="E76" s="170"/>
+      <c r="F76" s="170"/>
+      <c r="G76" s="170"/>
+      <c r="H76" s="170"/>
       <c r="I76" s="68"/>
       <c r="J76" s="67"/>
       <c r="K76" s="69"/>
@@ -6954,13 +6960,13 @@
     </row>
     <row r="77" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="67"/>
-      <c r="B77" s="124"/>
-      <c r="C77" s="124"/>
-      <c r="D77" s="124"/>
-      <c r="E77" s="124"/>
-      <c r="F77" s="124"/>
-      <c r="G77" s="124"/>
-      <c r="H77" s="124"/>
+      <c r="B77" s="170"/>
+      <c r="C77" s="170"/>
+      <c r="D77" s="170"/>
+      <c r="E77" s="170"/>
+      <c r="F77" s="170"/>
+      <c r="G77" s="170"/>
+      <c r="H77" s="170"/>
       <c r="I77" s="68"/>
       <c r="J77" s="67"/>
       <c r="K77" s="69"/>
@@ -6974,13 +6980,13 @@
     </row>
     <row r="78" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="67"/>
-      <c r="B78" s="124"/>
-      <c r="C78" s="124"/>
-      <c r="D78" s="124"/>
-      <c r="E78" s="124"/>
-      <c r="F78" s="124"/>
-      <c r="G78" s="124"/>
-      <c r="H78" s="124"/>
+      <c r="B78" s="170"/>
+      <c r="C78" s="170"/>
+      <c r="D78" s="170"/>
+      <c r="E78" s="170"/>
+      <c r="F78" s="170"/>
+      <c r="G78" s="170"/>
+      <c r="H78" s="170"/>
       <c r="I78" s="68"/>
       <c r="J78" s="67"/>
       <c r="K78" s="69"/>
@@ -6994,13 +7000,13 @@
     </row>
     <row r="79" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="67"/>
-      <c r="B79" s="124"/>
-      <c r="C79" s="124"/>
-      <c r="D79" s="124"/>
-      <c r="E79" s="124"/>
-      <c r="F79" s="124"/>
-      <c r="G79" s="124"/>
-      <c r="H79" s="124"/>
+      <c r="B79" s="170"/>
+      <c r="C79" s="170"/>
+      <c r="D79" s="170"/>
+      <c r="E79" s="170"/>
+      <c r="F79" s="170"/>
+      <c r="G79" s="170"/>
+      <c r="H79" s="170"/>
       <c r="I79" s="68"/>
       <c r="J79" s="67"/>
       <c r="K79" s="69"/>
@@ -7106,7 +7112,7 @@
       <c r="C84" s="71"/>
       <c r="D84" s="67"/>
       <c r="E84" s="67"/>
-      <c r="F84" s="125"/>
+      <c r="F84" s="103"/>
       <c r="G84" s="71"/>
       <c r="H84" s="67"/>
       <c r="I84" s="67"/>
@@ -7411,6 +7417,12 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B18:H18"/>
+    <mergeCell ref="D20:H20"/>
     <mergeCell ref="B60:H60"/>
     <mergeCell ref="A68:K68"/>
     <mergeCell ref="B70:H71"/>
@@ -7421,12 +7433,6 @@
     <mergeCell ref="B46:H46"/>
     <mergeCell ref="D48:H48"/>
     <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B18:H18"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="B21:C21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7457,40 +7463,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:60" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="126" t="s">
+      <c r="A1" s="104" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="126"/>
-      <c r="C1" s="126" t="s">
+      <c r="B1" s="104"/>
+      <c r="C1" s="104" t="s">
         <v>77</v>
       </c>
-      <c r="D1" s="126"/>
-      <c r="E1" s="174"/>
-      <c r="F1" s="175"/>
-      <c r="G1" s="175"/>
-      <c r="H1" s="175"/>
-      <c r="I1" s="175"/>
-      <c r="J1" s="175"/>
-      <c r="K1" s="127"/>
-      <c r="L1" s="127"/>
-      <c r="M1" s="128"/>
+      <c r="D1" s="104"/>
+      <c r="E1" s="142"/>
+      <c r="F1" s="143"/>
+      <c r="G1" s="143"/>
+      <c r="H1" s="143"/>
+      <c r="I1" s="143"/>
+      <c r="J1" s="143"/>
+      <c r="K1" s="105"/>
+      <c r="L1" s="105"/>
+      <c r="M1" s="106"/>
       <c r="N1" s="9"/>
       <c r="O1" s="4"/>
     </row>
     <row r="2" spans="1:60" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="126"/>
-      <c r="B2" s="126"/>
-      <c r="C2" s="129"/>
-      <c r="D2" s="126"/>
-      <c r="E2" s="126"/>
-      <c r="F2" s="126"/>
-      <c r="G2" s="126"/>
-      <c r="H2" s="126"/>
-      <c r="I2" s="126"/>
-      <c r="J2" s="126"/>
-      <c r="K2" s="126"/>
-      <c r="L2" s="126"/>
-      <c r="M2" s="130"/>
+      <c r="A2" s="104"/>
+      <c r="B2" s="104"/>
+      <c r="C2" s="107"/>
+      <c r="D2" s="104"/>
+      <c r="E2" s="104"/>
+      <c r="F2" s="104"/>
+      <c r="G2" s="104"/>
+      <c r="H2" s="104"/>
+      <c r="I2" s="104"/>
+      <c r="J2" s="104"/>
+      <c r="K2" s="104"/>
+      <c r="L2" s="104"/>
+      <c r="M2" s="108"/>
       <c r="N2" s="3"/>
       <c r="O2" s="4"/>
       <c r="P2" s="4"/>
@@ -7540,18 +7546,18 @@
       <c r="BH2" s="4"/>
     </row>
     <row r="3" spans="1:60" ht="3.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="131"/>
-      <c r="C3" s="132"/>
-      <c r="D3" s="133"/>
+      <c r="B3" s="109"/>
+      <c r="C3" s="110"/>
+      <c r="D3" s="111"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
-      <c r="I3" s="134"/>
-      <c r="J3" s="134"/>
-      <c r="K3" s="134"/>
+      <c r="I3" s="112"/>
+      <c r="J3" s="112"/>
+      <c r="K3" s="112"/>
       <c r="L3" s="1"/>
-      <c r="M3" s="135"/>
+      <c r="M3" s="113"/>
       <c r="N3" s="3"/>
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
@@ -7602,23 +7608,23 @@
     </row>
     <row r="4" spans="1:60" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="9"/>
-      <c r="C4" s="132"/>
-      <c r="D4" s="136"/>
+      <c r="C4" s="110"/>
+      <c r="D4" s="114"/>
       <c r="E4" s="5"/>
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
       <c r="H4" s="6"/>
       <c r="I4" s="14"/>
-      <c r="J4" s="137" t="s">
+      <c r="J4" s="115" t="s">
         <v>78</v>
       </c>
-      <c r="K4" s="137" t="s">
+      <c r="K4" s="115" t="s">
         <v>78</v>
       </c>
-      <c r="L4" s="137" t="s">
+      <c r="L4" s="115" t="s">
         <v>78</v>
       </c>
-      <c r="M4" s="138"/>
+      <c r="M4" s="116"/>
       <c r="N4" s="9"/>
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
@@ -7669,21 +7675,21 @@
     </row>
     <row r="5" spans="1:60" ht="35.1" customHeight="1" x14ac:dyDescent="0.7">
       <c r="B5" s="9"/>
-      <c r="C5" s="132"/>
-      <c r="D5" s="136"/>
+      <c r="C5" s="110"/>
+      <c r="D5" s="114"/>
       <c r="E5" s="10"/>
-      <c r="F5" s="139" t="s">
+      <c r="F5" s="117" t="s">
         <v>79</v>
       </c>
-      <c r="G5" s="140"/>
-      <c r="H5" s="141" t="s">
+      <c r="G5" s="118"/>
+      <c r="H5" s="119" t="s">
         <v>80</v>
       </c>
-      <c r="I5" s="141"/>
-      <c r="J5" s="141"/>
-      <c r="K5" s="141"/>
-      <c r="L5" s="141"/>
-      <c r="M5" s="142">
+      <c r="I5" s="119"/>
+      <c r="J5" s="119"/>
+      <c r="K5" s="119"/>
+      <c r="L5" s="119"/>
+      <c r="M5" s="120">
         <v>2024</v>
       </c>
       <c r="N5" s="9"/>
@@ -7736,8 +7742,8 @@
     </row>
     <row r="6" spans="1:60" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="9"/>
-      <c r="C6" s="132"/>
-      <c r="D6" s="136"/>
+      <c r="C6" s="110"/>
+      <c r="D6" s="114"/>
       <c r="E6" s="10"/>
       <c r="F6" s="14"/>
       <c r="G6" s="14"/>
@@ -7746,7 +7752,7 @@
       <c r="J6" s="14"/>
       <c r="K6" s="14"/>
       <c r="L6" s="14"/>
-      <c r="M6" s="135"/>
+      <c r="M6" s="113"/>
       <c r="N6" s="9"/>
       <c r="O6" s="4"/>
       <c r="P6" s="4"/>
@@ -7797,23 +7803,23 @@
     </row>
     <row r="7" spans="1:60" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="9"/>
-      <c r="C7" s="132"/>
-      <c r="D7" s="136"/>
+      <c r="C7" s="110"/>
+      <c r="D7" s="114"/>
       <c r="E7" s="10"/>
-      <c r="F7" s="176"/>
-      <c r="G7" s="176"/>
-      <c r="H7" s="176"/>
-      <c r="I7" s="143" t="s">
+      <c r="F7" s="144"/>
+      <c r="G7" s="144"/>
+      <c r="H7" s="144"/>
+      <c r="I7" s="187" t="s">
         <v>81</v>
       </c>
-      <c r="J7" s="143" t="s">
+      <c r="J7" s="187" t="s">
         <v>5</v>
       </c>
-      <c r="K7" s="143"/>
-      <c r="L7" s="144" t="s">
+      <c r="K7" s="187"/>
+      <c r="L7" s="179" t="s">
         <v>82</v>
       </c>
-      <c r="M7" s="145" t="s">
+      <c r="M7" s="180" t="s">
         <v>5</v>
       </c>
       <c r="N7" s="9"/>
@@ -7823,9 +7829,9 @@
       <c r="R7" s="4"/>
       <c r="S7" s="4"/>
       <c r="T7" s="4"/>
-      <c r="U7" s="146"/>
-      <c r="V7" s="146"/>
-      <c r="W7" s="146"/>
+      <c r="U7" s="188"/>
+      <c r="V7" s="188"/>
+      <c r="W7" s="188"/>
       <c r="AA7" s="4"/>
       <c r="AB7" s="4"/>
       <c r="AC7" s="4"/>
@@ -7861,37 +7867,37 @@
       <c r="BG7" s="4"/>
       <c r="BH7" s="4"/>
     </row>
-    <row r="8" spans="1:60" s="147" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B8" s="148"/>
-      <c r="C8" s="149"/>
-      <c r="D8" s="150"/>
-      <c r="E8" s="151"/>
-      <c r="F8" s="177"/>
-      <c r="G8" s="177"/>
-      <c r="H8" s="177"/>
-      <c r="I8" s="152">
+    <row r="8" spans="1:60" s="121" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B8" s="122"/>
+      <c r="C8" s="123"/>
+      <c r="D8" s="124"/>
+      <c r="E8" s="125"/>
+      <c r="F8" s="145"/>
+      <c r="G8" s="145"/>
+      <c r="H8" s="145"/>
+      <c r="I8" s="126">
         <v>1</v>
       </c>
-      <c r="J8" s="179" t="s">
+      <c r="J8" s="189" t="s">
         <v>83</v>
       </c>
-      <c r="K8" s="179"/>
-      <c r="L8" s="154">
+      <c r="K8" s="189"/>
+      <c r="L8" s="127">
         <v>1</v>
       </c>
-      <c r="M8" s="180" t="s">
+      <c r="M8" s="147" t="s">
         <v>87</v>
       </c>
-      <c r="N8" s="148"/>
+      <c r="N8" s="122"/>
       <c r="O8" s="77"/>
       <c r="P8" s="77"/>
       <c r="Q8" s="77"/>
       <c r="R8" s="77"/>
       <c r="S8" s="77"/>
       <c r="T8" s="77"/>
-      <c r="U8" s="156"/>
-      <c r="V8" s="157"/>
-      <c r="W8" s="157"/>
+      <c r="U8" s="129"/>
+      <c r="V8" s="183"/>
+      <c r="W8" s="183"/>
       <c r="AA8" s="77"/>
       <c r="AB8" s="77"/>
       <c r="AC8" s="77"/>
@@ -7927,37 +7933,37 @@
       <c r="BG8" s="77"/>
       <c r="BH8" s="77"/>
     </row>
-    <row r="9" spans="1:60" s="147" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B9" s="148"/>
-      <c r="C9" s="149"/>
-      <c r="D9" s="150"/>
-      <c r="E9" s="151"/>
-      <c r="F9" s="177"/>
-      <c r="G9" s="177"/>
-      <c r="H9" s="177"/>
-      <c r="I9" s="152">
+    <row r="9" spans="1:60" s="121" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B9" s="122"/>
+      <c r="C9" s="123"/>
+      <c r="D9" s="124"/>
+      <c r="E9" s="125"/>
+      <c r="F9" s="145"/>
+      <c r="G9" s="145"/>
+      <c r="H9" s="145"/>
+      <c r="I9" s="126">
         <v>2</v>
       </c>
-      <c r="J9" s="179" t="s">
+      <c r="J9" s="189" t="s">
         <v>85</v>
       </c>
-      <c r="K9" s="179"/>
-      <c r="L9" s="154">
+      <c r="K9" s="189"/>
+      <c r="L9" s="127">
         <v>2</v>
       </c>
-      <c r="M9" s="180" t="s">
+      <c r="M9" s="147" t="s">
         <v>72</v>
       </c>
-      <c r="N9" s="148"/>
+      <c r="N9" s="122"/>
       <c r="O9" s="77"/>
       <c r="P9" s="77"/>
       <c r="Q9" s="77"/>
       <c r="R9" s="77"/>
       <c r="S9" s="77"/>
       <c r="T9" s="77"/>
-      <c r="U9" s="156"/>
-      <c r="V9" s="157"/>
-      <c r="W9" s="157"/>
+      <c r="U9" s="129"/>
+      <c r="V9" s="183"/>
+      <c r="W9" s="183"/>
       <c r="AA9" s="77"/>
       <c r="AB9" s="77"/>
       <c r="AC9" s="77"/>
@@ -7993,37 +7999,37 @@
       <c r="BG9" s="77"/>
       <c r="BH9" s="77"/>
     </row>
-    <row r="10" spans="1:60" s="147" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B10" s="148"/>
-      <c r="C10" s="149"/>
-      <c r="D10" s="150"/>
-      <c r="E10" s="151"/>
-      <c r="F10" s="177"/>
-      <c r="G10" s="177"/>
-      <c r="H10" s="177"/>
-      <c r="I10" s="152">
+    <row r="10" spans="1:60" s="121" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B10" s="122"/>
+      <c r="C10" s="123"/>
+      <c r="D10" s="124"/>
+      <c r="E10" s="125"/>
+      <c r="F10" s="145"/>
+      <c r="G10" s="145"/>
+      <c r="H10" s="145"/>
+      <c r="I10" s="126">
         <v>3</v>
       </c>
-      <c r="J10" s="179" t="s">
+      <c r="J10" s="189" t="s">
         <v>86</v>
       </c>
-      <c r="K10" s="179"/>
-      <c r="L10" s="154">
+      <c r="K10" s="189"/>
+      <c r="L10" s="127">
         <v>3</v>
       </c>
-      <c r="M10" s="180" t="s">
+      <c r="M10" s="147" t="s">
         <v>47</v>
       </c>
-      <c r="N10" s="148"/>
+      <c r="N10" s="122"/>
       <c r="O10" s="77"/>
       <c r="P10" s="77"/>
       <c r="Q10" s="77"/>
       <c r="R10" s="77"/>
       <c r="S10" s="77"/>
       <c r="T10" s="77"/>
-      <c r="U10" s="156"/>
-      <c r="V10" s="157"/>
-      <c r="W10" s="157"/>
+      <c r="U10" s="129"/>
+      <c r="V10" s="183"/>
+      <c r="W10" s="183"/>
       <c r="AA10" s="77"/>
       <c r="AB10" s="77"/>
       <c r="AC10" s="77"/>
@@ -8059,37 +8065,37 @@
       <c r="BG10" s="77"/>
       <c r="BH10" s="77"/>
     </row>
-    <row r="11" spans="1:60" s="147" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B11" s="148"/>
-      <c r="C11" s="149"/>
-      <c r="D11" s="150"/>
-      <c r="E11" s="151"/>
-      <c r="F11" s="177"/>
-      <c r="G11" s="177"/>
-      <c r="H11" s="177"/>
-      <c r="I11" s="152">
+    <row r="11" spans="1:60" s="121" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B11" s="122"/>
+      <c r="C11" s="123"/>
+      <c r="D11" s="124"/>
+      <c r="E11" s="125"/>
+      <c r="F11" s="145"/>
+      <c r="G11" s="145"/>
+      <c r="H11" s="145"/>
+      <c r="I11" s="126">
         <v>4</v>
       </c>
-      <c r="J11" s="179" t="s">
+      <c r="J11" s="189" t="s">
         <v>53</v>
       </c>
-      <c r="K11" s="179"/>
-      <c r="L11" s="154">
+      <c r="K11" s="189"/>
+      <c r="L11" s="127">
         <v>4</v>
       </c>
-      <c r="M11" s="180" t="s">
+      <c r="M11" s="147" t="s">
         <v>50</v>
       </c>
-      <c r="N11" s="148"/>
+      <c r="N11" s="122"/>
       <c r="O11" s="77"/>
       <c r="P11" s="77"/>
       <c r="Q11" s="77"/>
       <c r="R11" s="77"/>
       <c r="S11" s="77"/>
       <c r="T11" s="77"/>
-      <c r="U11" s="156"/>
-      <c r="V11" s="157"/>
-      <c r="W11" s="157"/>
+      <c r="U11" s="129"/>
+      <c r="V11" s="183"/>
+      <c r="W11" s="183"/>
       <c r="AA11" s="77"/>
       <c r="AB11" s="77"/>
       <c r="AC11" s="77"/>
@@ -8125,37 +8131,37 @@
       <c r="BG11" s="77"/>
       <c r="BH11" s="77"/>
     </row>
-    <row r="12" spans="1:60" s="147" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B12" s="148"/>
-      <c r="C12" s="149"/>
-      <c r="D12" s="150"/>
-      <c r="E12" s="151"/>
-      <c r="F12" s="177"/>
-      <c r="G12" s="177"/>
-      <c r="H12" s="177"/>
-      <c r="I12" s="152">
+    <row r="12" spans="1:60" s="121" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B12" s="122"/>
+      <c r="C12" s="123"/>
+      <c r="D12" s="124"/>
+      <c r="E12" s="125"/>
+      <c r="F12" s="145"/>
+      <c r="G12" s="145"/>
+      <c r="H12" s="145"/>
+      <c r="I12" s="126">
         <v>5</v>
       </c>
-      <c r="J12" s="179" t="s">
+      <c r="J12" s="189" t="s">
         <v>51</v>
       </c>
-      <c r="K12" s="179"/>
-      <c r="L12" s="154">
+      <c r="K12" s="189"/>
+      <c r="L12" s="127">
         <v>5</v>
       </c>
-      <c r="M12" s="180" t="s">
+      <c r="M12" s="147" t="s">
         <v>88</v>
       </c>
-      <c r="N12" s="148"/>
+      <c r="N12" s="122"/>
       <c r="O12" s="77"/>
       <c r="P12" s="77"/>
       <c r="Q12" s="77"/>
       <c r="R12" s="77"/>
       <c r="S12" s="77"/>
       <c r="T12" s="77"/>
-      <c r="U12" s="156"/>
-      <c r="V12" s="157"/>
-      <c r="W12" s="157"/>
+      <c r="U12" s="129"/>
+      <c r="V12" s="183"/>
+      <c r="W12" s="183"/>
       <c r="AA12" s="77"/>
       <c r="AB12" s="77"/>
       <c r="AC12" s="77"/>
@@ -8191,33 +8197,33 @@
       <c r="BG12" s="77"/>
       <c r="BH12" s="77"/>
     </row>
-    <row r="13" spans="1:60" s="147" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B13" s="148"/>
-      <c r="C13" s="149"/>
-      <c r="D13" s="150"/>
-      <c r="E13" s="151"/>
-      <c r="F13" s="177"/>
-      <c r="G13" s="177"/>
-      <c r="H13" s="177"/>
-      <c r="I13" s="152">
+    <row r="13" spans="1:60" s="121" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B13" s="122"/>
+      <c r="C13" s="123"/>
+      <c r="D13" s="124"/>
+      <c r="E13" s="125"/>
+      <c r="F13" s="145"/>
+      <c r="G13" s="145"/>
+      <c r="H13" s="145"/>
+      <c r="I13" s="126">
         <v>6</v>
       </c>
-      <c r="J13" s="153"/>
-      <c r="K13" s="153"/>
-      <c r="L13" s="154">
+      <c r="J13" s="182"/>
+      <c r="K13" s="182"/>
+      <c r="L13" s="127">
         <v>6</v>
       </c>
-      <c r="M13" s="155"/>
-      <c r="N13" s="148"/>
+      <c r="M13" s="128"/>
+      <c r="N13" s="122"/>
       <c r="O13" s="77"/>
       <c r="P13" s="77"/>
       <c r="Q13" s="77"/>
       <c r="R13" s="77"/>
       <c r="S13" s="77"/>
       <c r="T13" s="77"/>
-      <c r="U13" s="156"/>
-      <c r="V13" s="157"/>
-      <c r="W13" s="157"/>
+      <c r="U13" s="129"/>
+      <c r="V13" s="183"/>
+      <c r="W13" s="183"/>
       <c r="AA13" s="77"/>
       <c r="AB13" s="77"/>
       <c r="AC13" s="77"/>
@@ -8253,33 +8259,33 @@
       <c r="BG13" s="77"/>
       <c r="BH13" s="77"/>
     </row>
-    <row r="14" spans="1:60" s="147" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B14" s="148"/>
-      <c r="C14" s="149"/>
-      <c r="D14" s="150"/>
-      <c r="E14" s="151"/>
-      <c r="F14" s="177"/>
-      <c r="G14" s="177"/>
-      <c r="H14" s="177"/>
-      <c r="I14" s="152">
+    <row r="14" spans="1:60" s="121" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B14" s="122"/>
+      <c r="C14" s="123"/>
+      <c r="D14" s="124"/>
+      <c r="E14" s="125"/>
+      <c r="F14" s="145"/>
+      <c r="G14" s="145"/>
+      <c r="H14" s="145"/>
+      <c r="I14" s="126">
         <v>7</v>
       </c>
-      <c r="J14" s="153"/>
-      <c r="K14" s="153"/>
-      <c r="L14" s="154">
+      <c r="J14" s="182"/>
+      <c r="K14" s="182"/>
+      <c r="L14" s="127">
         <v>7</v>
       </c>
-      <c r="M14" s="155"/>
-      <c r="N14" s="148"/>
+      <c r="M14" s="128"/>
+      <c r="N14" s="122"/>
       <c r="O14" s="77"/>
       <c r="P14" s="77"/>
       <c r="Q14" s="77"/>
       <c r="R14" s="77"/>
       <c r="S14" s="77"/>
       <c r="T14" s="77"/>
-      <c r="U14" s="156"/>
-      <c r="V14" s="157"/>
-      <c r="W14" s="157"/>
+      <c r="U14" s="129"/>
+      <c r="V14" s="183"/>
+      <c r="W14" s="183"/>
       <c r="AA14" s="77"/>
       <c r="AB14" s="77"/>
       <c r="AC14" s="77"/>
@@ -8315,33 +8321,33 @@
       <c r="BG14" s="77"/>
       <c r="BH14" s="77"/>
     </row>
-    <row r="15" spans="1:60" s="147" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B15" s="148"/>
-      <c r="C15" s="149"/>
-      <c r="D15" s="150"/>
-      <c r="E15" s="151"/>
-      <c r="F15" s="177"/>
-      <c r="G15" s="177"/>
-      <c r="H15" s="177"/>
-      <c r="I15" s="152">
+    <row r="15" spans="1:60" s="121" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B15" s="122"/>
+      <c r="C15" s="123"/>
+      <c r="D15" s="124"/>
+      <c r="E15" s="125"/>
+      <c r="F15" s="145"/>
+      <c r="G15" s="145"/>
+      <c r="H15" s="145"/>
+      <c r="I15" s="126">
         <v>8</v>
       </c>
-      <c r="J15" s="153"/>
-      <c r="K15" s="153"/>
-      <c r="L15" s="154">
+      <c r="J15" s="182"/>
+      <c r="K15" s="182"/>
+      <c r="L15" s="127">
         <v>8</v>
       </c>
-      <c r="M15" s="155"/>
-      <c r="N15" s="148"/>
+      <c r="M15" s="128"/>
+      <c r="N15" s="122"/>
       <c r="O15" s="77"/>
       <c r="P15" s="77"/>
       <c r="Q15" s="77"/>
       <c r="R15" s="77"/>
       <c r="S15" s="77"/>
       <c r="T15" s="77"/>
-      <c r="U15" s="156"/>
-      <c r="V15" s="157"/>
-      <c r="W15" s="157"/>
+      <c r="U15" s="129"/>
+      <c r="V15" s="183"/>
+      <c r="W15" s="183"/>
       <c r="AA15" s="77"/>
       <c r="AB15" s="77"/>
       <c r="AC15" s="77"/>
@@ -8377,33 +8383,33 @@
       <c r="BG15" s="77"/>
       <c r="BH15" s="77"/>
     </row>
-    <row r="16" spans="1:60" s="147" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B16" s="148"/>
-      <c r="C16" s="149"/>
-      <c r="D16" s="150"/>
-      <c r="E16" s="151"/>
-      <c r="F16" s="177"/>
-      <c r="G16" s="177"/>
-      <c r="H16" s="177"/>
-      <c r="I16" s="152">
+    <row r="16" spans="1:60" s="121" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B16" s="122"/>
+      <c r="C16" s="123"/>
+      <c r="D16" s="124"/>
+      <c r="E16" s="125"/>
+      <c r="F16" s="145"/>
+      <c r="G16" s="145"/>
+      <c r="H16" s="145"/>
+      <c r="I16" s="126">
         <v>9</v>
       </c>
-      <c r="J16" s="153"/>
-      <c r="K16" s="153"/>
-      <c r="L16" s="154">
+      <c r="J16" s="182"/>
+      <c r="K16" s="182"/>
+      <c r="L16" s="127">
         <v>9</v>
       </c>
-      <c r="M16" s="155"/>
-      <c r="N16" s="148"/>
+      <c r="M16" s="128"/>
+      <c r="N16" s="122"/>
       <c r="O16" s="77"/>
       <c r="P16" s="77"/>
       <c r="Q16" s="77"/>
       <c r="R16" s="77"/>
       <c r="S16" s="77"/>
       <c r="T16" s="77"/>
-      <c r="U16" s="156"/>
-      <c r="V16" s="157"/>
-      <c r="W16" s="157"/>
+      <c r="U16" s="129"/>
+      <c r="V16" s="183"/>
+      <c r="W16" s="183"/>
       <c r="AA16" s="77"/>
       <c r="AB16" s="77"/>
       <c r="AC16" s="77"/>
@@ -8439,33 +8445,33 @@
       <c r="BG16" s="77"/>
       <c r="BH16" s="77"/>
     </row>
-    <row r="17" spans="2:60" s="147" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B17" s="148"/>
-      <c r="C17" s="149"/>
-      <c r="D17" s="150"/>
-      <c r="E17" s="151"/>
-      <c r="F17" s="177"/>
-      <c r="G17" s="177"/>
-      <c r="H17" s="177"/>
-      <c r="I17" s="152">
+    <row r="17" spans="2:60" s="121" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B17" s="122"/>
+      <c r="C17" s="123"/>
+      <c r="D17" s="124"/>
+      <c r="E17" s="125"/>
+      <c r="F17" s="145"/>
+      <c r="G17" s="145"/>
+      <c r="H17" s="145"/>
+      <c r="I17" s="126">
         <v>10</v>
       </c>
-      <c r="J17" s="153"/>
-      <c r="K17" s="153"/>
-      <c r="L17" s="154">
+      <c r="J17" s="182"/>
+      <c r="K17" s="182"/>
+      <c r="L17" s="127">
         <v>10</v>
       </c>
-      <c r="M17" s="155"/>
-      <c r="N17" s="148"/>
+      <c r="M17" s="128"/>
+      <c r="N17" s="122"/>
       <c r="O17" s="77"/>
       <c r="P17" s="77"/>
       <c r="Q17" s="77"/>
       <c r="R17" s="77"/>
       <c r="S17" s="77"/>
       <c r="T17" s="77"/>
-      <c r="U17" s="156"/>
-      <c r="V17" s="157"/>
-      <c r="W17" s="157"/>
+      <c r="U17" s="129"/>
+      <c r="V17" s="183"/>
+      <c r="W17" s="183"/>
       <c r="AA17" s="77"/>
       <c r="AB17" s="77"/>
       <c r="AC17" s="77"/>
@@ -8503,17 +8509,17 @@
     </row>
     <row r="18" spans="2:60" ht="3.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="9"/>
-      <c r="C18" s="132"/>
-      <c r="D18" s="136"/>
+      <c r="C18" s="110"/>
+      <c r="D18" s="114"/>
       <c r="E18" s="10"/>
-      <c r="F18" s="158"/>
-      <c r="G18" s="158"/>
-      <c r="H18" s="158"/>
-      <c r="I18" s="159"/>
-      <c r="J18" s="159"/>
-      <c r="K18" s="159"/>
-      <c r="L18" s="160"/>
-      <c r="M18" s="161"/>
+      <c r="F18" s="130"/>
+      <c r="G18" s="130"/>
+      <c r="H18" s="130"/>
+      <c r="I18" s="131"/>
+      <c r="J18" s="131"/>
+      <c r="K18" s="131"/>
+      <c r="L18" s="132"/>
+      <c r="M18" s="133"/>
       <c r="N18" s="9"/>
       <c r="O18" s="4"/>
       <c r="P18" s="4"/>
@@ -8521,9 +8527,9 @@
       <c r="R18" s="4"/>
       <c r="S18" s="4"/>
       <c r="T18" s="4"/>
-      <c r="U18" s="121"/>
-      <c r="V18" s="121"/>
-      <c r="W18" s="162"/>
+      <c r="U18" s="101"/>
+      <c r="V18" s="101"/>
+      <c r="W18" s="134"/>
       <c r="AA18" s="4"/>
       <c r="AB18" s="4"/>
       <c r="AC18" s="4"/>
@@ -8561,19 +8567,19 @@
     </row>
     <row r="19" spans="2:60" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="9"/>
-      <c r="C19" s="132"/>
-      <c r="D19" s="136"/>
+      <c r="C19" s="110"/>
+      <c r="D19" s="114"/>
       <c r="E19" s="10"/>
-      <c r="F19" s="163" t="s">
+      <c r="F19" s="186" t="s">
         <v>5</v>
       </c>
-      <c r="G19" s="163"/>
-      <c r="H19" s="163"/>
-      <c r="I19" s="143"/>
-      <c r="J19" s="143"/>
-      <c r="K19" s="143"/>
+      <c r="G19" s="186"/>
+      <c r="H19" s="186"/>
+      <c r="I19" s="187"/>
+      <c r="J19" s="187"/>
+      <c r="K19" s="187"/>
       <c r="L19" s="1"/>
-      <c r="M19" s="135"/>
+      <c r="M19" s="113"/>
       <c r="N19" s="9"/>
       <c r="O19" s="4"/>
       <c r="P19" s="4"/>
@@ -8581,9 +8587,9 @@
       <c r="R19" s="4"/>
       <c r="S19" s="4"/>
       <c r="T19" s="4"/>
-      <c r="U19" s="121"/>
-      <c r="V19" s="121"/>
-      <c r="W19" s="121"/>
+      <c r="U19" s="101"/>
+      <c r="V19" s="101"/>
+      <c r="W19" s="101"/>
       <c r="X19" s="4"/>
       <c r="Y19" s="4"/>
       <c r="Z19" s="4"/>
@@ -8624,27 +8630,27 @@
     </row>
     <row r="20" spans="2:60" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B20" s="9"/>
-      <c r="C20" s="132"/>
-      <c r="D20" s="136"/>
+      <c r="C20" s="110"/>
+      <c r="D20" s="114"/>
       <c r="E20" s="10"/>
-      <c r="F20" s="164">
+      <c r="F20" s="135">
         <v>1</v>
       </c>
-      <c r="G20" s="185" t="s">
+      <c r="G20" s="184" t="s">
         <v>33</v>
       </c>
-      <c r="H20" s="185"/>
-      <c r="I20" s="152">
+      <c r="H20" s="184"/>
+      <c r="I20" s="126">
         <v>1</v>
       </c>
-      <c r="J20" s="181" t="s">
+      <c r="J20" s="185" t="s">
         <v>104</v>
       </c>
-      <c r="K20" s="181"/>
-      <c r="L20" s="178">
+      <c r="K20" s="185"/>
+      <c r="L20" s="146">
         <v>1</v>
       </c>
-      <c r="M20" s="182" t="s">
+      <c r="M20" s="148" t="s">
         <v>89</v>
       </c>
       <c r="N20" s="9"/>
@@ -8654,9 +8660,9 @@
       <c r="R20" s="4"/>
       <c r="S20" s="4"/>
       <c r="T20" s="4"/>
-      <c r="U20" s="146"/>
-      <c r="V20" s="146"/>
-      <c r="W20" s="146"/>
+      <c r="U20" s="188"/>
+      <c r="V20" s="188"/>
+      <c r="W20" s="188"/>
       <c r="X20" s="4"/>
       <c r="Y20" s="4"/>
       <c r="Z20" s="4"/>
@@ -8697,25 +8703,25 @@
     </row>
     <row r="21" spans="2:60" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B21" s="9"/>
-      <c r="C21" s="132"/>
-      <c r="D21" s="136"/>
+      <c r="C21" s="110"/>
+      <c r="D21" s="114"/>
       <c r="E21" s="10"/>
-      <c r="F21" s="164">
+      <c r="F21" s="135">
         <v>2</v>
       </c>
-      <c r="G21" s="185" t="s">
+      <c r="G21" s="184" t="s">
         <v>36</v>
       </c>
-      <c r="H21" s="185"/>
-      <c r="I21" s="152">
+      <c r="H21" s="184"/>
+      <c r="I21" s="126">
         <v>2</v>
       </c>
-      <c r="J21" s="181" t="s">
+      <c r="J21" s="185" t="s">
         <v>105</v>
       </c>
-      <c r="K21" s="181"/>
+      <c r="K21" s="185"/>
       <c r="L21" s="1"/>
-      <c r="M21" s="182" t="s">
+      <c r="M21" s="148" t="s">
         <v>90</v>
       </c>
       <c r="N21" s="9"/>
@@ -8725,9 +8731,9 @@
       <c r="R21" s="4"/>
       <c r="S21" s="4"/>
       <c r="T21" s="4"/>
-      <c r="U21" s="156"/>
-      <c r="V21" s="157"/>
-      <c r="W21" s="157"/>
+      <c r="U21" s="129"/>
+      <c r="V21" s="183"/>
+      <c r="W21" s="183"/>
       <c r="X21" s="4"/>
       <c r="Y21" s="4"/>
       <c r="Z21" s="4"/>
@@ -8768,25 +8774,25 @@
     </row>
     <row r="22" spans="2:60" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B22" s="9"/>
-      <c r="C22" s="132"/>
-      <c r="D22" s="136"/>
+      <c r="C22" s="110"/>
+      <c r="D22" s="114"/>
       <c r="E22" s="10"/>
-      <c r="F22" s="164">
+      <c r="F22" s="135">
         <v>3</v>
       </c>
-      <c r="G22" s="185" t="s">
+      <c r="G22" s="184" t="s">
         <v>34</v>
       </c>
-      <c r="H22" s="185"/>
-      <c r="I22" s="152">
+      <c r="H22" s="184"/>
+      <c r="I22" s="126">
         <v>3</v>
       </c>
-      <c r="J22" s="181" t="s">
+      <c r="J22" s="185" t="s">
         <v>106</v>
       </c>
-      <c r="K22" s="181"/>
+      <c r="K22" s="185"/>
       <c r="L22" s="1"/>
-      <c r="M22" s="182" t="s">
+      <c r="M22" s="148" t="s">
         <v>91</v>
       </c>
       <c r="N22" s="9"/>
@@ -8796,9 +8802,9 @@
       <c r="R22" s="4"/>
       <c r="S22" s="4"/>
       <c r="T22" s="4"/>
-      <c r="U22" s="156"/>
-      <c r="V22" s="157"/>
-      <c r="W22" s="157"/>
+      <c r="U22" s="129"/>
+      <c r="V22" s="183"/>
+      <c r="W22" s="183"/>
       <c r="X22" s="4"/>
       <c r="Y22" s="4"/>
       <c r="Z22" s="4"/>
@@ -8839,23 +8845,23 @@
     </row>
     <row r="23" spans="2:60" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B23" s="9"/>
-      <c r="C23" s="132"/>
-      <c r="D23" s="136"/>
+      <c r="C23" s="110"/>
+      <c r="D23" s="114"/>
       <c r="E23" s="10"/>
-      <c r="F23" s="164">
+      <c r="F23" s="135">
         <v>4</v>
       </c>
-      <c r="G23" s="185" t="s">
+      <c r="G23" s="184" t="s">
         <v>35</v>
       </c>
-      <c r="H23" s="185"/>
-      <c r="I23" s="152"/>
-      <c r="J23" s="181" t="s">
+      <c r="H23" s="184"/>
+      <c r="I23" s="126"/>
+      <c r="J23" s="185" t="s">
         <v>96</v>
       </c>
-      <c r="K23" s="181"/>
+      <c r="K23" s="185"/>
       <c r="L23" s="1"/>
-      <c r="M23" s="183"/>
+      <c r="M23" s="149"/>
       <c r="N23" s="9"/>
       <c r="O23" s="4"/>
       <c r="P23" s="4"/>
@@ -8863,9 +8869,9 @@
       <c r="R23" s="4"/>
       <c r="S23" s="4"/>
       <c r="T23" s="4"/>
-      <c r="U23" s="156"/>
-      <c r="V23" s="157"/>
-      <c r="W23" s="157"/>
+      <c r="U23" s="129"/>
+      <c r="V23" s="183"/>
+      <c r="W23" s="183"/>
       <c r="X23" s="4"/>
       <c r="Y23" s="4"/>
       <c r="Z23" s="4"/>
@@ -8906,23 +8912,23 @@
     </row>
     <row r="24" spans="2:60" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B24" s="9"/>
-      <c r="C24" s="132"/>
-      <c r="D24" s="136"/>
+      <c r="C24" s="110"/>
+      <c r="D24" s="114"/>
       <c r="E24" s="10"/>
-      <c r="F24" s="164">
+      <c r="F24" s="135">
         <v>5</v>
       </c>
-      <c r="G24" s="185" t="s">
+      <c r="G24" s="184" t="s">
         <v>32</v>
       </c>
-      <c r="H24" s="185"/>
-      <c r="I24" s="152"/>
-      <c r="J24" s="153"/>
-      <c r="K24" s="153"/>
-      <c r="L24" s="178">
+      <c r="H24" s="184"/>
+      <c r="I24" s="126"/>
+      <c r="J24" s="182"/>
+      <c r="K24" s="182"/>
+      <c r="L24" s="146">
         <v>2</v>
       </c>
-      <c r="M24" s="184" t="s">
+      <c r="M24" s="150" t="s">
         <v>92</v>
       </c>
       <c r="N24" s="9"/>
@@ -8932,9 +8938,9 @@
       <c r="R24" s="4"/>
       <c r="S24" s="4"/>
       <c r="T24" s="4"/>
-      <c r="U24" s="156"/>
-      <c r="V24" s="157"/>
-      <c r="W24" s="157"/>
+      <c r="U24" s="129"/>
+      <c r="V24" s="183"/>
+      <c r="W24" s="183"/>
       <c r="X24" s="4"/>
       <c r="Y24" s="4"/>
       <c r="Z24" s="4"/>
@@ -8975,19 +8981,19 @@
     </row>
     <row r="25" spans="2:60" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B25" s="9"/>
-      <c r="C25" s="132"/>
-      <c r="D25" s="136"/>
+      <c r="C25" s="110"/>
+      <c r="D25" s="114"/>
       <c r="E25" s="10"/>
-      <c r="F25" s="164">
+      <c r="F25" s="135">
         <v>6</v>
       </c>
-      <c r="G25" s="165"/>
-      <c r="H25" s="165"/>
-      <c r="I25" s="152"/>
-      <c r="J25" s="153"/>
-      <c r="K25" s="153"/>
-      <c r="L25" s="178"/>
-      <c r="M25" s="184" t="s">
+      <c r="G25" s="181"/>
+      <c r="H25" s="181"/>
+      <c r="I25" s="126"/>
+      <c r="J25" s="182"/>
+      <c r="K25" s="182"/>
+      <c r="L25" s="146"/>
+      <c r="M25" s="150" t="s">
         <v>93</v>
       </c>
       <c r="N25" s="9"/>
@@ -8997,9 +9003,9 @@
       <c r="R25" s="4"/>
       <c r="S25" s="4"/>
       <c r="T25" s="4"/>
-      <c r="U25" s="156"/>
-      <c r="V25" s="157"/>
-      <c r="W25" s="157"/>
+      <c r="U25" s="129"/>
+      <c r="V25" s="183"/>
+      <c r="W25" s="183"/>
       <c r="X25" s="4"/>
       <c r="Y25" s="4"/>
       <c r="Z25" s="4"/>
@@ -9040,19 +9046,19 @@
     </row>
     <row r="26" spans="2:60" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B26" s="9"/>
-      <c r="C26" s="132"/>
-      <c r="D26" s="136"/>
+      <c r="C26" s="110"/>
+      <c r="D26" s="114"/>
       <c r="E26" s="10"/>
-      <c r="F26" s="164">
+      <c r="F26" s="135">
         <v>7</v>
       </c>
-      <c r="G26" s="165"/>
-      <c r="H26" s="165"/>
-      <c r="I26" s="152"/>
-      <c r="J26" s="153"/>
-      <c r="K26" s="153"/>
-      <c r="L26" s="178"/>
-      <c r="M26" s="184" t="s">
+      <c r="G26" s="181"/>
+      <c r="H26" s="181"/>
+      <c r="I26" s="126"/>
+      <c r="J26" s="182"/>
+      <c r="K26" s="182"/>
+      <c r="L26" s="146"/>
+      <c r="M26" s="150" t="s">
         <v>94</v>
       </c>
       <c r="N26" s="9"/>
@@ -9062,9 +9068,9 @@
       <c r="R26" s="4"/>
       <c r="S26" s="4"/>
       <c r="T26" s="4"/>
-      <c r="U26" s="156"/>
-      <c r="V26" s="157"/>
-      <c r="W26" s="157"/>
+      <c r="U26" s="129"/>
+      <c r="V26" s="183"/>
+      <c r="W26" s="183"/>
       <c r="X26" s="4"/>
       <c r="Y26" s="4"/>
       <c r="Z26" s="4"/>
@@ -9105,19 +9111,19 @@
     </row>
     <row r="27" spans="2:60" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B27" s="9"/>
-      <c r="C27" s="132"/>
-      <c r="D27" s="136"/>
+      <c r="C27" s="110"/>
+      <c r="D27" s="114"/>
       <c r="E27" s="10"/>
-      <c r="F27" s="164">
+      <c r="F27" s="135">
         <v>8</v>
       </c>
-      <c r="G27" s="165"/>
-      <c r="H27" s="165"/>
-      <c r="I27" s="152"/>
-      <c r="J27" s="153"/>
-      <c r="K27" s="153"/>
-      <c r="L27" s="178"/>
-      <c r="M27" s="183"/>
+      <c r="G27" s="181"/>
+      <c r="H27" s="181"/>
+      <c r="I27" s="126"/>
+      <c r="J27" s="182"/>
+      <c r="K27" s="182"/>
+      <c r="L27" s="146"/>
+      <c r="M27" s="149"/>
       <c r="N27" s="9"/>
       <c r="O27" s="4"/>
       <c r="P27" s="4"/>
@@ -9125,9 +9131,9 @@
       <c r="R27" s="4"/>
       <c r="S27" s="4"/>
       <c r="T27" s="4"/>
-      <c r="U27" s="156"/>
-      <c r="V27" s="157"/>
-      <c r="W27" s="157"/>
+      <c r="U27" s="129"/>
+      <c r="V27" s="183"/>
+      <c r="W27" s="183"/>
       <c r="X27" s="4"/>
       <c r="Y27" s="4"/>
       <c r="Z27" s="4"/>
@@ -9168,21 +9174,21 @@
     </row>
     <row r="28" spans="2:60" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B28" s="9"/>
-      <c r="C28" s="132"/>
-      <c r="D28" s="136"/>
+      <c r="C28" s="110"/>
+      <c r="D28" s="114"/>
       <c r="E28" s="10"/>
-      <c r="F28" s="164">
+      <c r="F28" s="135">
         <v>9</v>
       </c>
-      <c r="G28" s="165"/>
-      <c r="H28" s="165"/>
-      <c r="I28" s="152"/>
-      <c r="J28" s="153"/>
-      <c r="K28" s="153"/>
-      <c r="L28" s="178">
+      <c r="G28" s="181"/>
+      <c r="H28" s="181"/>
+      <c r="I28" s="126"/>
+      <c r="J28" s="182"/>
+      <c r="K28" s="182"/>
+      <c r="L28" s="146">
         <v>3</v>
       </c>
-      <c r="M28" s="184" t="s">
+      <c r="M28" s="150" t="s">
         <v>95</v>
       </c>
       <c r="N28" s="9"/>
@@ -9192,9 +9198,9 @@
       <c r="R28" s="4"/>
       <c r="S28" s="4"/>
       <c r="T28" s="4"/>
-      <c r="U28" s="156"/>
-      <c r="V28" s="157"/>
-      <c r="W28" s="157"/>
+      <c r="U28" s="129"/>
+      <c r="V28" s="183"/>
+      <c r="W28" s="183"/>
       <c r="X28" s="4"/>
       <c r="Y28" s="4"/>
       <c r="Z28" s="4"/>
@@ -9235,19 +9241,19 @@
     </row>
     <row r="29" spans="2:60" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B29" s="9"/>
-      <c r="C29" s="132"/>
-      <c r="D29" s="136"/>
+      <c r="C29" s="110"/>
+      <c r="D29" s="114"/>
       <c r="E29" s="10"/>
-      <c r="F29" s="164">
+      <c r="F29" s="135">
         <v>10</v>
       </c>
-      <c r="G29" s="165"/>
-      <c r="H29" s="165"/>
-      <c r="I29" s="152"/>
-      <c r="J29" s="153"/>
-      <c r="K29" s="153"/>
+      <c r="G29" s="181"/>
+      <c r="H29" s="181"/>
+      <c r="I29" s="126"/>
+      <c r="J29" s="182"/>
+      <c r="K29" s="182"/>
       <c r="L29" s="1"/>
-      <c r="M29" s="184" t="s">
+      <c r="M29" s="150" t="s">
         <v>107</v>
       </c>
       <c r="N29" s="9"/>
@@ -9257,9 +9263,9 @@
       <c r="R29" s="4"/>
       <c r="S29" s="4"/>
       <c r="T29" s="4"/>
-      <c r="U29" s="156"/>
-      <c r="V29" s="157"/>
-      <c r="W29" s="157"/>
+      <c r="U29" s="129"/>
+      <c r="V29" s="183"/>
+      <c r="W29" s="183"/>
       <c r="X29" s="4"/>
       <c r="Y29" s="4"/>
       <c r="Z29" s="4"/>
@@ -9300,19 +9306,19 @@
     </row>
     <row r="30" spans="2:60" ht="29.4" x14ac:dyDescent="0.3">
       <c r="B30" s="9"/>
-      <c r="C30" s="132"/>
-      <c r="D30" s="136"/>
+      <c r="C30" s="110"/>
+      <c r="D30" s="114"/>
       <c r="E30" s="4"/>
-      <c r="F30" s="166" t="s">
+      <c r="F30" s="178" t="s">
         <v>6</v>
       </c>
-      <c r="G30" s="166"/>
-      <c r="H30" s="166"/>
+      <c r="G30" s="178"/>
+      <c r="H30" s="178"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
-      <c r="L30" s="144"/>
-      <c r="M30" s="145"/>
+      <c r="L30" s="179"/>
+      <c r="M30" s="180"/>
       <c r="N30" s="9"/>
       <c r="O30" s="9"/>
       <c r="P30" s="9"/>
@@ -9363,27 +9369,27 @@
     </row>
     <row r="31" spans="2:60" ht="23.4" x14ac:dyDescent="0.45">
       <c r="B31" s="9"/>
-      <c r="C31" s="132"/>
-      <c r="D31" s="136"/>
+      <c r="C31" s="110"/>
+      <c r="D31" s="114"/>
       <c r="E31" s="4"/>
-      <c r="F31" s="167">
+      <c r="F31" s="136">
         <v>1</v>
       </c>
-      <c r="G31" s="186" t="s">
+      <c r="G31" s="176" t="s">
         <v>74</v>
       </c>
-      <c r="H31" s="186"/>
-      <c r="I31" s="178">
+      <c r="H31" s="176"/>
+      <c r="I31" s="146">
         <v>1</v>
       </c>
-      <c r="J31" s="187" t="s">
+      <c r="J31" s="151" t="s">
         <v>97</v>
       </c>
-      <c r="K31" s="188"/>
-      <c r="L31" s="154">
+      <c r="K31" s="152"/>
+      <c r="L31" s="127">
         <v>1</v>
       </c>
-      <c r="M31" s="180" t="s">
+      <c r="M31" s="147" t="s">
         <v>109</v>
       </c>
       <c r="N31" s="9"/>
@@ -9436,27 +9442,27 @@
     </row>
     <row r="32" spans="2:60" ht="23.4" x14ac:dyDescent="0.45">
       <c r="B32" s="9"/>
-      <c r="C32" s="132"/>
-      <c r="D32" s="136"/>
+      <c r="C32" s="110"/>
+      <c r="D32" s="114"/>
       <c r="E32" s="4"/>
-      <c r="F32" s="167">
+      <c r="F32" s="136">
         <v>2</v>
       </c>
-      <c r="G32" s="186" t="s">
+      <c r="G32" s="176" t="s">
         <v>37</v>
       </c>
-      <c r="H32" s="186"/>
-      <c r="I32" s="178">
+      <c r="H32" s="176"/>
+      <c r="I32" s="146">
         <v>2</v>
       </c>
-      <c r="J32" s="187" t="s">
+      <c r="J32" s="151" t="s">
         <v>103</v>
       </c>
-      <c r="K32" s="188"/>
-      <c r="L32" s="154">
+      <c r="K32" s="152"/>
+      <c r="L32" s="127">
         <v>2</v>
       </c>
-      <c r="M32" s="180" t="s">
+      <c r="M32" s="147" t="s">
         <v>99</v>
       </c>
       <c r="N32" s="9"/>
@@ -9509,25 +9515,25 @@
     </row>
     <row r="33" spans="2:60" ht="27" x14ac:dyDescent="0.6">
       <c r="B33" s="9"/>
-      <c r="C33" s="132"/>
-      <c r="D33" s="136"/>
+      <c r="C33" s="110"/>
+      <c r="D33" s="114"/>
       <c r="E33" s="4"/>
-      <c r="F33" s="167">
+      <c r="F33" s="136">
         <v>3</v>
       </c>
-      <c r="G33" s="186" t="s">
+      <c r="G33" s="176" t="s">
         <v>73</v>
       </c>
-      <c r="H33" s="186"/>
-      <c r="I33" s="178">
+      <c r="H33" s="176"/>
+      <c r="I33" s="146">
         <v>3</v>
       </c>
-      <c r="J33" s="187" t="s">
+      <c r="J33" s="151" t="s">
         <v>98</v>
       </c>
-      <c r="K33" s="188"/>
-      <c r="L33" s="154"/>
-      <c r="M33" s="189" t="s">
+      <c r="K33" s="152"/>
+      <c r="L33" s="127"/>
+      <c r="M33" s="153" t="s">
         <v>108</v>
       </c>
       <c r="N33" s="9"/>
@@ -9580,25 +9586,25 @@
     </row>
     <row r="34" spans="2:60" ht="23.4" x14ac:dyDescent="0.45">
       <c r="B34" s="4"/>
-      <c r="C34" s="132"/>
-      <c r="D34" s="136"/>
+      <c r="C34" s="110"/>
+      <c r="D34" s="114"/>
       <c r="E34" s="4"/>
-      <c r="F34" s="167">
+      <c r="F34" s="136">
         <v>4</v>
       </c>
-      <c r="G34" s="186" t="s">
+      <c r="G34" s="176" t="s">
         <v>27</v>
       </c>
-      <c r="H34" s="186"/>
+      <c r="H34" s="176"/>
       <c r="I34" s="1"/>
-      <c r="J34" s="187" t="s">
+      <c r="J34" s="151" t="s">
         <v>102</v>
       </c>
-      <c r="K34" s="188"/>
-      <c r="L34" s="154">
+      <c r="K34" s="152"/>
+      <c r="L34" s="127">
         <v>3</v>
       </c>
-      <c r="M34" s="180" t="s">
+      <c r="M34" s="147" t="s">
         <v>100</v>
       </c>
       <c r="N34" s="4"/>
@@ -9651,25 +9657,25 @@
     </row>
     <row r="35" spans="2:60" ht="23.4" x14ac:dyDescent="0.45">
       <c r="B35" s="4"/>
-      <c r="C35" s="132"/>
-      <c r="D35" s="136"/>
+      <c r="C35" s="110"/>
+      <c r="D35" s="114"/>
       <c r="E35" s="4"/>
-      <c r="F35" s="167">
+      <c r="F35" s="136">
         <v>5</v>
       </c>
-      <c r="G35" s="186" t="s">
+      <c r="G35" s="176" t="s">
         <v>75</v>
       </c>
-      <c r="H35" s="186"/>
+      <c r="H35" s="176"/>
       <c r="I35" s="1">
         <v>4</v>
       </c>
-      <c r="J35" s="187" t="s">
+      <c r="J35" s="151" t="s">
         <v>101</v>
       </c>
-      <c r="K35" s="188"/>
-      <c r="L35" s="154"/>
-      <c r="M35" s="155"/>
+      <c r="K35" s="152"/>
+      <c r="L35" s="127"/>
+      <c r="M35" s="128"/>
       <c r="N35" s="4"/>
       <c r="O35" s="4"/>
       <c r="P35" s="4"/>
@@ -9720,21 +9726,21 @@
     </row>
     <row r="36" spans="2:60" ht="23.4" x14ac:dyDescent="0.45">
       <c r="B36" s="4"/>
-      <c r="C36" s="132"/>
-      <c r="D36" s="136"/>
+      <c r="C36" s="110"/>
+      <c r="D36" s="114"/>
       <c r="E36" s="4"/>
-      <c r="F36" s="167">
+      <c r="F36" s="136">
         <v>6</v>
       </c>
-      <c r="G36" s="186" t="s">
+      <c r="G36" s="176" t="s">
         <v>76</v>
       </c>
-      <c r="H36" s="186"/>
+      <c r="H36" s="176"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
-      <c r="L36" s="154"/>
-      <c r="M36" s="155"/>
+      <c r="L36" s="127"/>
+      <c r="M36" s="128"/>
       <c r="N36" s="4"/>
       <c r="O36" s="4"/>
       <c r="P36" s="4"/>
@@ -9785,19 +9791,19 @@
     </row>
     <row r="37" spans="2:60" ht="20.399999999999999" x14ac:dyDescent="0.45">
       <c r="B37" s="4"/>
-      <c r="C37" s="132"/>
-      <c r="D37" s="136"/>
+      <c r="C37" s="110"/>
+      <c r="D37" s="114"/>
       <c r="E37" s="4"/>
-      <c r="F37" s="167">
+      <c r="F37" s="136">
         <v>7</v>
       </c>
-      <c r="G37" s="168"/>
-      <c r="H37" s="168"/>
+      <c r="G37" s="177"/>
+      <c r="H37" s="177"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
-      <c r="L37" s="154"/>
-      <c r="M37" s="155"/>
+      <c r="L37" s="127"/>
+      <c r="M37" s="128"/>
       <c r="N37" s="4"/>
       <c r="O37" s="4"/>
       <c r="P37" s="4"/>
@@ -9848,19 +9854,19 @@
     </row>
     <row r="38" spans="2:60" ht="20.399999999999999" x14ac:dyDescent="0.45">
       <c r="B38" s="4"/>
-      <c r="C38" s="132"/>
-      <c r="D38" s="136"/>
+      <c r="C38" s="110"/>
+      <c r="D38" s="114"/>
       <c r="E38" s="4"/>
-      <c r="F38" s="167">
+      <c r="F38" s="136">
         <v>8</v>
       </c>
-      <c r="G38" s="168"/>
-      <c r="H38" s="168"/>
+      <c r="G38" s="177"/>
+      <c r="H38" s="177"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
-      <c r="L38" s="154"/>
-      <c r="M38" s="155"/>
+      <c r="L38" s="127"/>
+      <c r="M38" s="128"/>
       <c r="N38" s="4"/>
       <c r="O38" s="4"/>
       <c r="P38" s="4"/>
@@ -9911,19 +9917,19 @@
     </row>
     <row r="39" spans="2:60" ht="20.399999999999999" x14ac:dyDescent="0.45">
       <c r="B39" s="4"/>
-      <c r="C39" s="132"/>
-      <c r="D39" s="136"/>
+      <c r="C39" s="110"/>
+      <c r="D39" s="114"/>
       <c r="E39" s="4"/>
-      <c r="F39" s="167">
+      <c r="F39" s="136">
         <v>9</v>
       </c>
-      <c r="G39" s="168"/>
-      <c r="H39" s="168"/>
+      <c r="G39" s="177"/>
+      <c r="H39" s="177"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
-      <c r="L39" s="154"/>
-      <c r="M39" s="155"/>
+      <c r="L39" s="127"/>
+      <c r="M39" s="128"/>
       <c r="N39" s="4"/>
       <c r="O39" s="4"/>
       <c r="P39" s="4"/>
@@ -9974,19 +9980,19 @@
     </row>
     <row r="40" spans="2:60" ht="20.399999999999999" x14ac:dyDescent="0.45">
       <c r="B40" s="4"/>
-      <c r="C40" s="132"/>
-      <c r="D40" s="136"/>
+      <c r="C40" s="110"/>
+      <c r="D40" s="114"/>
       <c r="E40" s="4"/>
-      <c r="F40" s="167">
+      <c r="F40" s="136">
         <v>10</v>
       </c>
-      <c r="G40" s="168"/>
-      <c r="H40" s="168"/>
+      <c r="G40" s="177"/>
+      <c r="H40" s="177"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
-      <c r="K40" s="136"/>
-      <c r="L40" s="154"/>
-      <c r="M40" s="155"/>
+      <c r="K40" s="114"/>
+      <c r="L40" s="127"/>
+      <c r="M40" s="128"/>
       <c r="N40" s="4"/>
       <c r="O40" s="4"/>
       <c r="P40" s="4"/>
@@ -10037,17 +10043,17 @@
     </row>
     <row r="41" spans="2:60" x14ac:dyDescent="0.3">
       <c r="B41" s="4"/>
-      <c r="C41" s="169"/>
-      <c r="D41" s="170"/>
-      <c r="E41" s="171"/>
-      <c r="F41" s="171"/>
-      <c r="G41" s="171"/>
-      <c r="H41" s="171"/>
-      <c r="I41" s="171"/>
-      <c r="J41" s="171"/>
-      <c r="K41" s="171"/>
-      <c r="L41" s="171"/>
-      <c r="M41" s="172"/>
+      <c r="C41" s="137"/>
+      <c r="D41" s="138"/>
+      <c r="E41" s="139"/>
+      <c r="F41" s="139"/>
+      <c r="G41" s="139"/>
+      <c r="H41" s="139"/>
+      <c r="I41" s="139"/>
+      <c r="J41" s="139"/>
+      <c r="K41" s="139"/>
+      <c r="L41" s="139"/>
+      <c r="M41" s="140"/>
       <c r="N41" s="4"/>
       <c r="O41" s="4"/>
       <c r="P41" s="4"/>
@@ -10163,7 +10169,7 @@
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
       <c r="F43" s="4"/>
-      <c r="G43" s="173" t="s">
+      <c r="G43" s="141" t="s">
         <v>84</v>
       </c>
       <c r="H43" s="4"/>
@@ -19311,47 +19317,23 @@
     </row>
   </sheetData>
   <mergeCells count="67">
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="G39:H39"/>
-    <mergeCell ref="G40:H40"/>
-    <mergeCell ref="F30:H30"/>
-    <mergeCell ref="L30:M30"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="V28:W28"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="V29:W29"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="V26:W26"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="V27:W27"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="V24:W24"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="V25:W25"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="V22:W22"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="V23:W23"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="U20:W20"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="U7:W7"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="V8:W8"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="V9:W9"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="V10:W10"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="V11:W11"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="V12:W12"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="V13:W13"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="V14:W14"/>
     <mergeCell ref="G21:H21"/>
     <mergeCell ref="J21:K21"/>
     <mergeCell ref="V21:W21"/>
@@ -19361,23 +19343,47 @@
     <mergeCell ref="V16:W16"/>
     <mergeCell ref="J17:K17"/>
     <mergeCell ref="V17:W17"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="V12:W12"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="V13:W13"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="V14:W14"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="V9:W9"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="V10:W10"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="V11:W11"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="L7:M7"/>
-    <mergeCell ref="U7:W7"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="V8:W8"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="U20:W20"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="V22:W22"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="V23:W23"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="V24:W24"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="V25:W25"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="V26:W26"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="V27:W27"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="V28:W28"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="V29:W29"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="L30:M30"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="G39:H39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
